--- a/labelled_dataset.xlsx
+++ b/labelled_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,30 +451,70 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>cpu_ctx_switches</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_interrupts</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_soft_interrupts</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_sys_calls</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>cpu_frequency</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>total_memory</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>available_memory</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>memory_percentage_usage</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_virtual_memory</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>available_virtual_memory</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>virtual_memory_percentage_usage</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>swap_total_memory</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>swap_available_memory</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>swap_used_memory</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>swap_memory_percentage_usage</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>battery_percentage</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>power_plugged</t>
         </is>
@@ -482,2245 +522,4177 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10971.78125</v>
+        <v>28058.9375</v>
       </c>
       <c r="B2" t="n">
-        <v>465319.6875</v>
+        <v>1184168.734375</v>
       </c>
       <c r="C2" t="n">
-        <v>467.25</v>
+        <v>1099.875</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>4.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>659905095</v>
       </c>
       <c r="F2" t="n">
-        <v>15.6518669128418</v>
+        <v>431628026</v>
       </c>
       <c r="G2" t="n">
-        <v>5.991321563720703</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J2" t="b">
+        <v>3204735767</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.845165252685547</v>
+      </c>
+      <c r="L2" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>78</v>
+      </c>
+      <c r="R2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10971.828125</v>
+        <v>28059.015625</v>
       </c>
       <c r="B3" t="n">
-        <v>465323.703125</v>
+        <v>1184175.1875</v>
       </c>
       <c r="C3" t="n">
-        <v>467.25</v>
+        <v>1099.875</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E3" t="inlineStr">
+        <v>5.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>659909831</v>
+      </c>
+      <c r="F3" t="n">
+        <v>431631262</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3204807540</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.989906311035156</v>
-      </c>
-      <c r="H3" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>44</v>
-      </c>
-      <c r="J3" t="b">
+      <c r="J3" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.854942321777344</v>
+      </c>
+      <c r="L3" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>78</v>
+      </c>
+      <c r="R3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10972.015625</v>
+        <v>28059.078125</v>
       </c>
       <c r="B4" t="n">
-        <v>465327.515625</v>
+        <v>1184179.296875</v>
       </c>
       <c r="C4" t="n">
-        <v>467.25</v>
+        <v>1099.875</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>3.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>659912482</v>
       </c>
       <c r="F4" t="n">
-        <v>15.6518669128418</v>
+        <v>431632797</v>
       </c>
       <c r="G4" t="n">
-        <v>6.002910614013672</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>44</v>
-      </c>
-      <c r="J4" t="b">
+        <v>3204814810</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.85504150390625</v>
+      </c>
+      <c r="L4" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>78</v>
+      </c>
+      <c r="R4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10972.125</v>
+        <v>28059.21875</v>
       </c>
       <c r="B5" t="n">
-        <v>465331.484375</v>
+        <v>1184183.40625</v>
       </c>
       <c r="C5" t="n">
-        <v>467.25</v>
+        <v>1099.875</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>4.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>659915695</v>
       </c>
       <c r="F5" t="n">
-        <v>15.6518669128418</v>
+        <v>431634774</v>
       </c>
       <c r="G5" t="n">
-        <v>6.002799987792969</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>44</v>
-      </c>
-      <c r="J5" t="b">
+        <v>3204825133</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.854934692382812</v>
+      </c>
+      <c r="L5" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>78</v>
+      </c>
+      <c r="R5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10972.203125</v>
+        <v>28059.25</v>
       </c>
       <c r="B6" t="n">
-        <v>465335.515625</v>
+        <v>1184187.578125</v>
       </c>
       <c r="C6" t="n">
-        <v>467.25</v>
+        <v>1099.875</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>659918885</v>
       </c>
       <c r="F6" t="n">
-        <v>15.6518669128418</v>
+        <v>431636594</v>
       </c>
       <c r="G6" t="n">
-        <v>6.002914428710938</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>44</v>
-      </c>
-      <c r="J6" t="b">
+        <v>3204834846</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.854972839355469</v>
+      </c>
+      <c r="L6" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>78</v>
+      </c>
+      <c r="R6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10972.328125</v>
+        <v>28059.3125</v>
       </c>
       <c r="B7" t="n">
-        <v>465339.28125</v>
+        <v>1184191.65625</v>
       </c>
       <c r="C7" t="n">
-        <v>467.25</v>
+        <v>1099.875</v>
       </c>
       <c r="D7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E7" t="inlineStr">
+        <v>3.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>659922144</v>
+      </c>
+      <c r="F7" t="n">
+        <v>431638678</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3204845063</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.002021789550781</v>
-      </c>
-      <c r="H7" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>44</v>
-      </c>
-      <c r="J7" t="b">
+      <c r="J7" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.860157012939453</v>
+      </c>
+      <c r="L7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>78</v>
+      </c>
+      <c r="R7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10972.40625</v>
+        <v>28059.359375</v>
       </c>
       <c r="B8" t="n">
-        <v>465343.375</v>
+        <v>1184195.71875</v>
       </c>
       <c r="C8" t="n">
-        <v>467.25</v>
+        <v>1099.875</v>
       </c>
       <c r="D8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>5.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>659925338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>431640794</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3204856372</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6.003803253173828</v>
-      </c>
-      <c r="H8" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>44</v>
-      </c>
-      <c r="J8" t="b">
+      <c r="J8" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.855014801025391</v>
+      </c>
+      <c r="L8" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>78</v>
+      </c>
+      <c r="R8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10972.515625</v>
+        <v>28059.359375</v>
       </c>
       <c r="B9" t="n">
-        <v>465347.1875</v>
+        <v>1184199.6875</v>
       </c>
       <c r="C9" t="n">
-        <v>467.3125</v>
+        <v>1099.875</v>
       </c>
       <c r="D9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>3.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>659928225</v>
+      </c>
+      <c r="F9" t="n">
+        <v>431642517</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3204867508</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.002017974853516</v>
-      </c>
-      <c r="H9" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>44</v>
-      </c>
-      <c r="J9" t="b">
+      <c r="J9" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.855060577392578</v>
+      </c>
+      <c r="L9" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>78</v>
+      </c>
+      <c r="R9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10972.546875</v>
+        <v>28059.359375</v>
       </c>
       <c r="B10" t="n">
-        <v>465351.046875</v>
+        <v>1184203.859375</v>
       </c>
       <c r="C10" t="n">
-        <v>467.3125</v>
+        <v>1099.90625</v>
       </c>
       <c r="D10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>2.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>659930970</v>
       </c>
       <c r="F10" t="n">
-        <v>15.6518669128418</v>
+        <v>431644156</v>
       </c>
       <c r="G10" t="n">
-        <v>6.002288818359375</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>44</v>
-      </c>
-      <c r="J10" t="b">
+        <v>3204875142</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.857219696044922</v>
+      </c>
+      <c r="L10" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>78</v>
+      </c>
+      <c r="R10" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10972.5625</v>
+        <v>28059.390625</v>
       </c>
       <c r="B11" t="n">
-        <v>465355.046875</v>
+        <v>1184207.875</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3125</v>
+        <v>1099.90625</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E11" t="inlineStr">
+        <v>4.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>659934201</v>
+      </c>
+      <c r="F11" t="n">
+        <v>431646061</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3204885112</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.001571655273438</v>
-      </c>
-      <c r="H11" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>44</v>
-      </c>
-      <c r="J11" t="b">
+      <c r="J11" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.857322692871094</v>
+      </c>
+      <c r="L11" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>78</v>
+      </c>
+      <c r="R11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10972.671875</v>
+        <v>28059.4375</v>
       </c>
       <c r="B12" t="n">
-        <v>465359.015625</v>
+        <v>1184211.96875</v>
       </c>
       <c r="C12" t="n">
-        <v>467.34375</v>
+        <v>1099.90625</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E12" t="inlineStr">
+        <v>3.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>659936587</v>
+      </c>
+      <c r="F12" t="n">
+        <v>431647396</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3204892741</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.003227233886719</v>
-      </c>
-      <c r="H12" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>44</v>
-      </c>
-      <c r="J12" t="b">
+      <c r="J12" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.856803894042969</v>
+      </c>
+      <c r="L12" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>78</v>
+      </c>
+      <c r="R12" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10972.734375</v>
+        <v>28059.53125</v>
       </c>
       <c r="B13" t="n">
-        <v>465362.96875</v>
+        <v>1184216.046875</v>
       </c>
       <c r="C13" t="n">
-        <v>467.34375</v>
+        <v>1099.90625</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
+        <v>3.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>659939568</v>
+      </c>
+      <c r="F13" t="n">
+        <v>431649199</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3204901437</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6.001811981201172</v>
-      </c>
-      <c r="H13" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>44</v>
-      </c>
-      <c r="J13" t="b">
+      <c r="J13" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.858325958251953</v>
+      </c>
+      <c r="L13" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>78</v>
+      </c>
+      <c r="R13" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10972.765625</v>
+        <v>28059.59375</v>
       </c>
       <c r="B14" t="n">
-        <v>465367.140625</v>
+        <v>1184220.328125</v>
       </c>
       <c r="C14" t="n">
-        <v>467.34375</v>
+        <v>1099.90625</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E14" t="inlineStr">
+        <v>3.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>659944473</v>
+      </c>
+      <c r="F14" t="n">
+        <v>431652079</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3204913018</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6.011795043945312</v>
-      </c>
-      <c r="H14" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>44</v>
-      </c>
-      <c r="J14" t="b">
+      <c r="J14" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.854274749755859</v>
+      </c>
+      <c r="L14" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>78</v>
+      </c>
+      <c r="R14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10972.8125</v>
+        <v>28059.625</v>
       </c>
       <c r="B15" t="n">
-        <v>465371.140625</v>
+        <v>1184224.34375</v>
       </c>
       <c r="C15" t="n">
-        <v>467.34375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E15" t="inlineStr">
+        <v>3.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>659953272</v>
+      </c>
+      <c r="F15" t="n">
+        <v>431657199</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3204932433</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6.004421234130859</v>
-      </c>
-      <c r="H15" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>44</v>
-      </c>
-      <c r="J15" t="b">
+      <c r="J15" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.863655090332031</v>
+      </c>
+      <c r="L15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>78</v>
+      </c>
+      <c r="R15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10972.8125</v>
+        <v>28059.6875</v>
       </c>
       <c r="B16" t="n">
-        <v>465375.203125</v>
+        <v>1184228.359375</v>
       </c>
       <c r="C16" t="n">
-        <v>467.359375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E16" t="inlineStr">
+        <v>5.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>659958788</v>
+      </c>
+      <c r="F16" t="n">
+        <v>431660505</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3204946616</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6.005550384521484</v>
-      </c>
-      <c r="H16" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>44</v>
-      </c>
-      <c r="J16" t="b">
+      <c r="J16" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.857765197753906</v>
+      </c>
+      <c r="L16" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>78</v>
+      </c>
+      <c r="R16" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10972.828125</v>
+        <v>28060.703125</v>
       </c>
       <c r="B17" t="n">
-        <v>465379.21875</v>
+        <v>1184231.234375</v>
       </c>
       <c r="C17" t="n">
-        <v>467.359375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E17" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="E17" t="n">
+        <v>659971650</v>
+      </c>
+      <c r="F17" t="n">
+        <v>431667764</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3204990706</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6.006191253662109</v>
-      </c>
-      <c r="H17" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>44</v>
-      </c>
-      <c r="J17" t="b">
+      <c r="J17" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.822486877441406</v>
+      </c>
+      <c r="L17" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>78</v>
+      </c>
+      <c r="R17" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10972.953125</v>
+        <v>28060.765625</v>
       </c>
       <c r="B18" t="n">
-        <v>465383.09375</v>
+        <v>1184235.109375</v>
       </c>
       <c r="C18" t="n">
-        <v>467.359375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>5.7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>659978899</v>
       </c>
       <c r="F18" t="n">
-        <v>15.6518669128418</v>
+        <v>431672316</v>
       </c>
       <c r="G18" t="n">
-        <v>6.007003784179688</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>44</v>
-      </c>
-      <c r="J18" t="b">
+        <v>3205011931</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.810859680175781</v>
+      </c>
+      <c r="L18" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>78</v>
+      </c>
+      <c r="R18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10972.984375</v>
+        <v>28060.796875</v>
       </c>
       <c r="B19" t="n">
-        <v>465387.125</v>
+        <v>1184239.203125</v>
       </c>
       <c r="C19" t="n">
-        <v>467.359375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E19" t="inlineStr">
+        <v>4.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>659985460</v>
+      </c>
+      <c r="F19" t="n">
+        <v>431676329</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3205033717</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6.008110046386719</v>
-      </c>
-      <c r="H19" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>44</v>
-      </c>
-      <c r="J19" t="b">
+      <c r="J19" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.817241668701172</v>
+      </c>
+      <c r="L19" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>78</v>
+      </c>
+      <c r="R19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10973.015625</v>
+        <v>28060.984375</v>
       </c>
       <c r="B20" t="n">
-        <v>465391.15625</v>
+        <v>1184243.171875</v>
       </c>
       <c r="C20" t="n">
-        <v>467.359375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>6.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>659997617</v>
       </c>
       <c r="F20" t="n">
-        <v>15.6518669128418</v>
+        <v>431683016</v>
       </c>
       <c r="G20" t="n">
-        <v>6.009086608886719</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>44</v>
-      </c>
-      <c r="J20" t="b">
+        <v>3205071770</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.799247741699219</v>
+      </c>
+      <c r="L20" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>78</v>
+      </c>
+      <c r="R20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10973.03125</v>
+        <v>28061.0625</v>
       </c>
       <c r="B21" t="n">
-        <v>465395.234375</v>
+        <v>1184247.15625</v>
       </c>
       <c r="C21" t="n">
-        <v>467.375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E21" t="inlineStr">
+        <v>4.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>660003967</v>
+      </c>
+      <c r="F21" t="n">
+        <v>431686692</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3205089741</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.007915496826172</v>
-      </c>
-      <c r="H21" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>44</v>
-      </c>
-      <c r="J21" t="b">
+      <c r="J21" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.815174102783203</v>
+      </c>
+      <c r="L21" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>78</v>
+      </c>
+      <c r="R21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10973.078125</v>
+        <v>28061.0625</v>
       </c>
       <c r="B22" t="n">
-        <v>465399.21875</v>
+        <v>1184251.296875</v>
       </c>
       <c r="C22" t="n">
-        <v>467.375</v>
+        <v>1099.921875</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>1.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>660009568</v>
+      </c>
+      <c r="F22" t="n">
+        <v>431689857</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3205103475</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.011360168457031</v>
-      </c>
-      <c r="H22" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>44</v>
-      </c>
-      <c r="J22" t="b">
+      <c r="J22" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.813056945800781</v>
+      </c>
+      <c r="L22" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>78</v>
+      </c>
+      <c r="R22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10973.109375</v>
+        <v>28061.1875</v>
       </c>
       <c r="B23" t="n">
-        <v>465403.21875</v>
+        <v>1184255.375</v>
       </c>
       <c r="C23" t="n">
-        <v>467.375</v>
+        <v>1099.9375</v>
       </c>
       <c r="D23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E23" t="inlineStr">
+        <v>5.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>660015168</v>
+      </c>
+      <c r="F23" t="n">
+        <v>431692966</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3205116708</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.005702972412109</v>
-      </c>
-      <c r="H23" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I23" t="n">
-        <v>44</v>
-      </c>
-      <c r="J23" t="b">
+      <c r="J23" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.813217163085938</v>
+      </c>
+      <c r="L23" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>78</v>
+      </c>
+      <c r="R23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10973.125</v>
+        <v>28061.25</v>
       </c>
       <c r="B24" t="n">
-        <v>465407.296875</v>
+        <v>1184259.5</v>
       </c>
       <c r="C24" t="n">
-        <v>467.375</v>
+        <v>1099.953125</v>
       </c>
       <c r="D24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E24" t="inlineStr">
+        <v>3.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>660025818</v>
+      </c>
+      <c r="F24" t="n">
+        <v>431699115</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3205139230</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.008365631103516</v>
-      </c>
-      <c r="H24" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I24" t="n">
-        <v>44</v>
-      </c>
-      <c r="J24" t="b">
+      <c r="J24" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.816024780273438</v>
+      </c>
+      <c r="L24" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>78</v>
+      </c>
+      <c r="R24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10973.21875</v>
+        <v>28061.296875</v>
       </c>
       <c r="B25" t="n">
-        <v>465411.09375</v>
+        <v>1184263.515625</v>
       </c>
       <c r="C25" t="n">
-        <v>467.390625</v>
+        <v>1099.953125</v>
       </c>
       <c r="D25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E25" t="inlineStr">
+        <v>4.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>660032174</v>
+      </c>
+      <c r="F25" t="n">
+        <v>431702719</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3205154149</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6.002300262451172</v>
-      </c>
-      <c r="H25" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I25" t="n">
-        <v>44</v>
-      </c>
-      <c r="J25" t="b">
+      <c r="J25" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.963249206542969</v>
+      </c>
+      <c r="L25" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>78</v>
+      </c>
+      <c r="R25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10973.25</v>
+        <v>28061.359375</v>
       </c>
       <c r="B26" t="n">
-        <v>465415.1875</v>
+        <v>1184267.5625</v>
       </c>
       <c r="C26" t="n">
-        <v>467.390625</v>
+        <v>1099.953125</v>
       </c>
       <c r="D26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>3.4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>660035489</v>
       </c>
       <c r="F26" t="n">
-        <v>15.6518669128418</v>
+        <v>431704628</v>
       </c>
       <c r="G26" t="n">
-        <v>6.00506591796875</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>44</v>
-      </c>
-      <c r="J26" t="b">
+        <v>3205165541</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.965782165527344</v>
+      </c>
+      <c r="L26" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>78</v>
+      </c>
+      <c r="R26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10973.296875</v>
+        <v>28061.5</v>
       </c>
       <c r="B27" t="n">
-        <v>465419.140625</v>
+        <v>1184271.671875</v>
       </c>
       <c r="C27" t="n">
-        <v>467.390625</v>
+        <v>1099.96875</v>
       </c>
       <c r="D27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>5.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>660038630</v>
       </c>
       <c r="F27" t="n">
-        <v>15.6518669128418</v>
+        <v>431706492</v>
       </c>
       <c r="G27" t="n">
-        <v>6.004215240478516</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I27" t="n">
-        <v>44</v>
-      </c>
-      <c r="J27" t="b">
+        <v>3205178880</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.966110229492188</v>
+      </c>
+      <c r="L27" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="M27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>78</v>
+      </c>
+      <c r="R27" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10973.40625</v>
+        <v>28061.5</v>
       </c>
       <c r="B28" t="n">
-        <v>465423.046875</v>
+        <v>1184275.765625</v>
       </c>
       <c r="C28" t="n">
-        <v>467.390625</v>
+        <v>1099.984375</v>
       </c>
       <c r="D28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E28" t="inlineStr">
+        <v>3.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>660040741</v>
+      </c>
+      <c r="F28" t="n">
+        <v>431707703</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3205187184</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G28" t="n">
-        <v>6.008003234863281</v>
-      </c>
-      <c r="H28" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I28" t="n">
-        <v>44</v>
-      </c>
-      <c r="J28" t="b">
+      <c r="J28" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.969722747802734</v>
+      </c>
+      <c r="L28" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="M28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>78</v>
+      </c>
+      <c r="R28" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10973.484375</v>
+        <v>28061.546875</v>
       </c>
       <c r="B29" t="n">
-        <v>465426.921875</v>
+        <v>1184279.890625</v>
       </c>
       <c r="C29" t="n">
-        <v>467.390625</v>
+        <v>1099.984375</v>
       </c>
       <c r="D29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E29" t="inlineStr">
+        <v>2.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>660043034</v>
+      </c>
+      <c r="F29" t="n">
+        <v>431709048</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3205193487</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.004127502441406</v>
-      </c>
-      <c r="H29" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>44</v>
-      </c>
-      <c r="J29" t="b">
+      <c r="J29" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.969181060791016</v>
+      </c>
+      <c r="L29" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>78</v>
+      </c>
+      <c r="R29" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10973.53125</v>
+        <v>28061.59375</v>
       </c>
       <c r="B30" t="n">
-        <v>465430.96875</v>
+        <v>1184283.9375</v>
       </c>
       <c r="C30" t="n">
-        <v>467.40625</v>
+        <v>1099.984375</v>
       </c>
       <c r="D30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E30" t="inlineStr">
+        <v>5.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>660046292</v>
+      </c>
+      <c r="F30" t="n">
+        <v>431710538</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3205204874</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G30" t="n">
-        <v>6.004650115966797</v>
-      </c>
-      <c r="H30" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I30" t="n">
-        <v>44</v>
-      </c>
-      <c r="J30" t="b">
+      <c r="J30" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.980728149414063</v>
+      </c>
+      <c r="L30" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>78</v>
+      </c>
+      <c r="R30" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10973.546875</v>
+        <v>28061.765625</v>
       </c>
       <c r="B31" t="n">
-        <v>465435</v>
+        <v>1184288.078125</v>
       </c>
       <c r="C31" t="n">
-        <v>467.40625</v>
+        <v>1099.984375</v>
       </c>
       <c r="D31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E31" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>660049956</v>
+      </c>
+      <c r="F31" t="n">
+        <v>431712315</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3205216110</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6.004055023193359</v>
-      </c>
-      <c r="H31" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I31" t="n">
-        <v>44</v>
-      </c>
-      <c r="J31" t="b">
+      <c r="J31" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.978839874267578</v>
+      </c>
+      <c r="L31" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>78</v>
+      </c>
+      <c r="R31" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>10973.5625</v>
+        <v>28061.875</v>
       </c>
       <c r="B32" t="n">
-        <v>465438.953125</v>
+        <v>1184292.140625</v>
       </c>
       <c r="C32" t="n">
-        <v>467.4375</v>
+        <v>1099.984375</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E32" t="inlineStr">
+        <v>4.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>660052535</v>
+      </c>
+      <c r="F32" t="n">
+        <v>431713940</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3205225176</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6.004768371582031</v>
-      </c>
-      <c r="H32" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I32" t="n">
-        <v>44</v>
-      </c>
-      <c r="J32" t="b">
+      <c r="J32" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6.000785827636719</v>
+      </c>
+      <c r="L32" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>78</v>
+      </c>
+      <c r="R32" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10973.59375</v>
+        <v>28062.03125</v>
       </c>
       <c r="B33" t="n">
-        <v>465443</v>
+        <v>1184296.109375</v>
       </c>
       <c r="C33" t="n">
-        <v>467.4375</v>
+        <v>1099.984375</v>
       </c>
       <c r="D33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E33" t="inlineStr">
+        <v>6.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>660055235</v>
+      </c>
+      <c r="F33" t="n">
+        <v>431715607</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3205233287</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6.004192352294922</v>
-      </c>
-      <c r="H33" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I33" t="n">
-        <v>44</v>
-      </c>
-      <c r="J33" t="b">
+      <c r="J33" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.998779296875</v>
+      </c>
+      <c r="L33" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>78</v>
+      </c>
+      <c r="R33" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>10973.65625</v>
+        <v>28062.046875</v>
       </c>
       <c r="B34" t="n">
-        <v>465446.953125</v>
+        <v>1184300.25</v>
       </c>
       <c r="C34" t="n">
-        <v>467.4375</v>
+        <v>1099.984375</v>
       </c>
       <c r="D34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E34" t="inlineStr">
+        <v>1.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>660058271</v>
+      </c>
+      <c r="F34" t="n">
+        <v>431717461</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3205242078</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G34" t="n">
-        <v>6.004531860351562</v>
-      </c>
-      <c r="H34" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I34" t="n">
-        <v>44</v>
-      </c>
-      <c r="J34" t="b">
+      <c r="J34" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6.040550231933594</v>
+      </c>
+      <c r="L34" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>78</v>
+      </c>
+      <c r="R34" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10974.25</v>
+        <v>28062.171875</v>
       </c>
       <c r="B35" t="n">
-        <v>465450.3125</v>
+        <v>1184304.359375</v>
       </c>
       <c r="C35" t="n">
-        <v>467.4375</v>
+        <v>1100.015625</v>
       </c>
       <c r="D35" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="E35" t="inlineStr">
+        <v>6.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>660060928</v>
+      </c>
+      <c r="F35" t="n">
+        <v>431718943</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3205250533</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G35" t="n">
-        <v>5.965919494628906</v>
-      </c>
-      <c r="H35" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="I35" t="n">
-        <v>44</v>
-      </c>
-      <c r="J35" t="b">
+      <c r="J35" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6.039424896240234</v>
+      </c>
+      <c r="L35" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>78</v>
+      </c>
+      <c r="R35" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10974.3125</v>
+        <v>28062.21875</v>
       </c>
       <c r="B36" t="n">
-        <v>465454.15625</v>
+        <v>1184308.40625</v>
       </c>
       <c r="C36" t="n">
-        <v>467.4375</v>
+        <v>1100.03125</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>3.4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>660063442</v>
       </c>
       <c r="F36" t="n">
-        <v>15.6518669128418</v>
+        <v>431720323</v>
       </c>
       <c r="G36" t="n">
-        <v>5.970867156982422</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="I36" t="n">
-        <v>44</v>
-      </c>
-      <c r="J36" t="b">
+        <v>3205258550</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.043949127197266</v>
+      </c>
+      <c r="L36" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>78</v>
+      </c>
+      <c r="R36" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>10974.375</v>
+        <v>28062.28125</v>
       </c>
       <c r="B37" t="n">
-        <v>465458.015625</v>
+        <v>1184312.421875</v>
       </c>
       <c r="C37" t="n">
-        <v>467.453125</v>
+        <v>1100.03125</v>
       </c>
       <c r="D37" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>5.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>660066458</v>
       </c>
       <c r="F37" t="n">
-        <v>15.6518669128418</v>
+        <v>431722112</v>
       </c>
       <c r="G37" t="n">
-        <v>5.968437194824219</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="I37" t="n">
-        <v>44</v>
-      </c>
-      <c r="J37" t="b">
+        <v>3205269519</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6.042564392089844</v>
+      </c>
+      <c r="L37" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>78</v>
+      </c>
+      <c r="R37" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>10974.515625</v>
+        <v>28062.328125</v>
       </c>
       <c r="B38" t="n">
-        <v>465461.796875</v>
+        <v>1184316.53125</v>
       </c>
       <c r="C38" t="n">
-        <v>467.453125</v>
+        <v>1100.03125</v>
       </c>
       <c r="D38" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>3.3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>660069046</v>
       </c>
       <c r="F38" t="n">
-        <v>15.6518669128418</v>
+        <v>431723583</v>
       </c>
       <c r="G38" t="n">
-        <v>5.961395263671875</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="I38" t="n">
-        <v>44</v>
-      </c>
-      <c r="J38" t="b">
+        <v>3205279452</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6.047542572021484</v>
+      </c>
+      <c r="L38" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>78</v>
+      </c>
+      <c r="R38" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10974.921875</v>
+        <v>28062.359375</v>
       </c>
       <c r="B39" t="n">
-        <v>465465.25</v>
+        <v>1184320.734375</v>
       </c>
       <c r="C39" t="n">
-        <v>467.46875</v>
+        <v>1100.03125</v>
       </c>
       <c r="D39" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>3.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>660072766</v>
       </c>
       <c r="F39" t="n">
-        <v>15.6518669128418</v>
+        <v>431725238</v>
       </c>
       <c r="G39" t="n">
-        <v>5.785308837890625</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>63</v>
-      </c>
-      <c r="I39" t="n">
-        <v>44</v>
-      </c>
-      <c r="J39" t="b">
+        <v>3205291466</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6.045230865478516</v>
+      </c>
+      <c r="L39" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>78</v>
+      </c>
+      <c r="R39" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10975.0625</v>
+        <v>28062.453125</v>
       </c>
       <c r="B40" t="n">
-        <v>465469.09375</v>
+        <v>1184324.71875</v>
       </c>
       <c r="C40" t="n">
-        <v>467.46875</v>
+        <v>1100.03125</v>
       </c>
       <c r="D40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>660076048</v>
       </c>
       <c r="F40" t="n">
-        <v>15.6518669128418</v>
+        <v>431726856</v>
       </c>
       <c r="G40" t="n">
-        <v>5.716827392578125</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>44</v>
-      </c>
-      <c r="J40" t="b">
+        <v>3205301749</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6.048263549804688</v>
+      </c>
+      <c r="L40" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>78</v>
+      </c>
+      <c r="R40" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10975.21875</v>
+        <v>28062.5</v>
       </c>
       <c r="B41" t="n">
-        <v>465472.875</v>
+        <v>1184328.921875</v>
       </c>
       <c r="C41" t="n">
-        <v>467.46875</v>
+        <v>1100.046875</v>
       </c>
       <c r="D41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>4.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>660078710</v>
       </c>
       <c r="F41" t="n">
-        <v>15.6518669128418</v>
+        <v>431728454</v>
       </c>
       <c r="G41" t="n">
-        <v>5.711193084716797</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="I41" t="n">
-        <v>44</v>
-      </c>
-      <c r="J41" t="b">
+        <v>3205309717</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K41" t="n">
+        <v>6.048774719238281</v>
+      </c>
+      <c r="L41" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>78</v>
+      </c>
+      <c r="R41" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10975.375</v>
+        <v>28062.5625</v>
       </c>
       <c r="B42" t="n">
-        <v>465476.734375</v>
+        <v>1184332.859375</v>
       </c>
       <c r="C42" t="n">
-        <v>467.484375</v>
+        <v>1100.0625</v>
       </c>
       <c r="D42" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>5.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>660081209</v>
       </c>
       <c r="F42" t="n">
-        <v>15.6518669128418</v>
+        <v>431729818</v>
       </c>
       <c r="G42" t="n">
-        <v>5.676383972167969</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="I42" t="n">
-        <v>44</v>
-      </c>
-      <c r="J42" t="b">
+        <v>3205317734</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K42" t="n">
+        <v>6.050922393798828</v>
+      </c>
+      <c r="L42" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>78</v>
+      </c>
+      <c r="R42" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10975.4375</v>
+        <v>28062.609375</v>
       </c>
       <c r="B43" t="n">
-        <v>465480.71875</v>
+        <v>1184337.03125</v>
       </c>
       <c r="C43" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" t="inlineStr">
+        <v>3.6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>660083977</v>
+      </c>
+      <c r="F43" t="n">
+        <v>431731455</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3205326221</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5.662605285644531</v>
-      </c>
-      <c r="H43" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="I43" t="n">
-        <v>44</v>
-      </c>
-      <c r="J43" t="b">
+      <c r="J43" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6.052959442138672</v>
+      </c>
+      <c r="L43" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>78</v>
+      </c>
+      <c r="R43" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>10975.5</v>
+        <v>28062.65625</v>
       </c>
       <c r="B44" t="n">
-        <v>465484.625</v>
+        <v>1184341.15625</v>
       </c>
       <c r="C44" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>2.9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>660086435</v>
       </c>
       <c r="F44" t="n">
-        <v>15.6518669128418</v>
+        <v>431732788</v>
       </c>
       <c r="G44" t="n">
-        <v>5.663562774658203</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="I44" t="n">
-        <v>44</v>
-      </c>
-      <c r="J44" t="b">
+        <v>3205333144</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K44" t="n">
+        <v>6.0531005859375</v>
+      </c>
+      <c r="L44" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>78</v>
+      </c>
+      <c r="R44" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10975.8125</v>
+        <v>28062.671875</v>
       </c>
       <c r="B45" t="n">
-        <v>465488.46875</v>
+        <v>1184345.328125</v>
       </c>
       <c r="C45" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D45" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E45" t="inlineStr">
+        <v>1.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>660089412</v>
+      </c>
+      <c r="F45" t="n">
+        <v>431734204</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3205342201</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5.612747192382812</v>
-      </c>
-      <c r="H45" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>44</v>
-      </c>
-      <c r="J45" t="b">
+      <c r="J45" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K45" t="n">
+        <v>6.051860809326172</v>
+      </c>
+      <c r="L45" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M45" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>78</v>
+      </c>
+      <c r="R45" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10975.859375</v>
+        <v>28063.28125</v>
       </c>
       <c r="B46" t="n">
-        <v>465492.46875</v>
+        <v>1184348.90625</v>
       </c>
       <c r="C46" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D46" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E46" t="inlineStr">
+        <v>16.2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>660091980</v>
+      </c>
+      <c r="F46" t="n">
+        <v>431735738</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3205351709</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G46" t="n">
-        <v>5.621437072753906</v>
-      </c>
-      <c r="H46" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="I46" t="n">
-        <v>44</v>
-      </c>
-      <c r="J46" t="b">
+      <c r="J46" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6.065330505371094</v>
+      </c>
+      <c r="L46" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N46" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>78</v>
+      </c>
+      <c r="R46" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10976.1875</v>
+        <v>28063.375</v>
       </c>
       <c r="B47" t="n">
-        <v>465496.21875</v>
+        <v>1184352.953125</v>
       </c>
       <c r="C47" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D47" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>5.2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>660094885</v>
       </c>
       <c r="F47" t="n">
-        <v>15.6518669128418</v>
+        <v>431737383</v>
       </c>
       <c r="G47" t="n">
-        <v>5.597049713134766</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>44</v>
-      </c>
-      <c r="J47" t="b">
+        <v>3205363551</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6.060649871826172</v>
+      </c>
+      <c r="L47" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N47" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>78</v>
+      </c>
+      <c r="R47" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10976.625</v>
+        <v>28063.421875</v>
       </c>
       <c r="B48" t="n">
-        <v>465499.609375</v>
+        <v>1184357.265625</v>
       </c>
       <c r="C48" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D48" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="E48" t="inlineStr">
+        <v>2.1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>660098300</v>
+      </c>
+      <c r="F48" t="n">
+        <v>431739090</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3205374716</v>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5.569717407226562</v>
-      </c>
-      <c r="H48" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>44</v>
-      </c>
-      <c r="J48" t="b">
+      <c r="J48" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6.063083648681641</v>
+      </c>
+      <c r="L48" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>78</v>
+      </c>
+      <c r="R48" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10976.984375</v>
+        <v>28063.484375</v>
       </c>
       <c r="B49" t="n">
-        <v>465503.234375</v>
+        <v>1184361.375</v>
       </c>
       <c r="C49" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D49" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E49" t="inlineStr">
+        <v>3.3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>660101005</v>
+      </c>
+      <c r="F49" t="n">
+        <v>431740724</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3205383140</v>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G49" t="n">
-        <v>5.544475555419922</v>
-      </c>
-      <c r="H49" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>44</v>
-      </c>
-      <c r="J49" t="b">
+      <c r="J49" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K49" t="n">
+        <v>6.060886383056641</v>
+      </c>
+      <c r="L49" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>78</v>
+      </c>
+      <c r="R49" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10977.359375</v>
+        <v>28063.53125</v>
       </c>
       <c r="B50" t="n">
-        <v>465507.015625</v>
+        <v>1184365.5</v>
       </c>
       <c r="C50" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D50" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="E50" t="inlineStr">
+        <v>3.6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>660103683</v>
+      </c>
+      <c r="F50" t="n">
+        <v>431742333</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3205391306</v>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G50" t="n">
-        <v>5.531887054443359</v>
-      </c>
-      <c r="H50" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="I50" t="n">
-        <v>44</v>
-      </c>
-      <c r="J50" t="b">
+      <c r="J50" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6.063846588134766</v>
+      </c>
+      <c r="L50" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N50" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>78</v>
+      </c>
+      <c r="R50" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10977.765625</v>
+        <v>28063.609375</v>
       </c>
       <c r="B51" t="n">
-        <v>465510.671875</v>
+        <v>1184369.453125</v>
       </c>
       <c r="C51" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D51" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="E51" t="inlineStr">
+        <v>4.9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>660106374</v>
+      </c>
+      <c r="F51" t="n">
+        <v>431743904</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3205399178</v>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.513687133789063</v>
-      </c>
-      <c r="H51" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="I51" t="n">
-        <v>44</v>
-      </c>
-      <c r="J51" t="b">
+      <c r="J51" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6.06646728515625</v>
+      </c>
+      <c r="L51" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N51" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>78</v>
+      </c>
+      <c r="R51" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10978.171875</v>
+        <v>28063.625</v>
       </c>
       <c r="B52" t="n">
-        <v>465514.046875</v>
+        <v>1184373.671875</v>
       </c>
       <c r="C52" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D52" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>2.9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>660109121</v>
       </c>
       <c r="F52" t="n">
-        <v>15.6518669128418</v>
+        <v>431745528</v>
       </c>
       <c r="G52" t="n">
-        <v>5.485755920410156</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>65</v>
-      </c>
-      <c r="I52" t="n">
-        <v>44</v>
-      </c>
-      <c r="J52" t="b">
+        <v>3205407530</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K52" t="n">
+        <v>6.067905426025391</v>
+      </c>
+      <c r="L52" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>78</v>
+      </c>
+      <c r="R52" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10978.390625</v>
+        <v>28063.71875</v>
       </c>
       <c r="B53" t="n">
-        <v>465518.078125</v>
+        <v>1184377.703125</v>
       </c>
       <c r="C53" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D53" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>4.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>660111801</v>
       </c>
       <c r="F53" t="n">
-        <v>15.6518669128418</v>
+        <v>431747074</v>
       </c>
       <c r="G53" t="n">
-        <v>5.458770751953125</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="I53" t="n">
-        <v>44</v>
-      </c>
-      <c r="J53" t="b">
+        <v>3205414865</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K53" t="n">
+        <v>6.066219329833984</v>
+      </c>
+      <c r="L53" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N53" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>78</v>
+      </c>
+      <c r="R53" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10979.875</v>
+        <v>28063.734375</v>
       </c>
       <c r="B54" t="n">
-        <v>465520.34375</v>
+        <v>1184381.90625</v>
       </c>
       <c r="C54" t="n">
-        <v>467.484375</v>
+        <v>1100.078125</v>
       </c>
       <c r="D54" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="E54" t="inlineStr">
+        <v>2.9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>660114607</v>
+      </c>
+      <c r="F54" t="n">
+        <v>431748679</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3205423663</v>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G54" t="n">
-        <v>5.465541839599609</v>
-      </c>
-      <c r="H54" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>44</v>
-      </c>
-      <c r="J54" t="b">
+      <c r="J54" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6.068202972412109</v>
+      </c>
+      <c r="L54" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N54" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>78</v>
+      </c>
+      <c r="R54" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10980.0625</v>
+        <v>28063.8125</v>
       </c>
       <c r="B55" t="n">
-        <v>465524.109375</v>
+        <v>1184386.03125</v>
       </c>
       <c r="C55" t="n">
-        <v>467.515625</v>
+        <v>1100.078125</v>
       </c>
       <c r="D55" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="E55" t="inlineStr">
+        <v>3.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>660117025</v>
+      </c>
+      <c r="F55" t="n">
+        <v>431750093</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3205432242</v>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G55" t="n">
-        <v>5.467636108398438</v>
-      </c>
-      <c r="H55" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="I55" t="n">
-        <v>44</v>
-      </c>
-      <c r="J55" t="b">
+      <c r="J55" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K55" t="n">
+        <v>6.066337585449219</v>
+      </c>
+      <c r="L55" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>78</v>
+      </c>
+      <c r="R55" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10980.34375</v>
+        <v>28063.890625</v>
       </c>
       <c r="B56" t="n">
-        <v>465527.234375</v>
+        <v>1184390.1875</v>
       </c>
       <c r="C56" t="n">
-        <v>467.546875</v>
+        <v>1100.078125</v>
       </c>
       <c r="D56" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E56" t="n">
+        <v>660120321</v>
       </c>
       <c r="F56" t="n">
-        <v>15.6518669128418</v>
+        <v>431752082</v>
       </c>
       <c r="G56" t="n">
-        <v>5.591278076171875</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="I56" t="n">
-        <v>44</v>
-      </c>
-      <c r="J56" t="b">
+        <v>3205443357</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K56" t="n">
+        <v>6.069866180419922</v>
+      </c>
+      <c r="L56" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>78</v>
+      </c>
+      <c r="R56" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10980.46875</v>
+        <v>28063.921875</v>
       </c>
       <c r="B57" t="n">
-        <v>465531.125</v>
+        <v>1184394.15625</v>
       </c>
       <c r="C57" t="n">
-        <v>467.546875</v>
+        <v>1100.09375</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>5.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>660123629</v>
       </c>
       <c r="F57" t="n">
-        <v>15.6518669128418</v>
+        <v>431753823</v>
       </c>
       <c r="G57" t="n">
-        <v>5.587177276611328</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="I57" t="n">
-        <v>44</v>
-      </c>
-      <c r="J57" t="b">
+        <v>3205455015</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K57" t="n">
+        <v>6.066532135009766</v>
+      </c>
+      <c r="L57" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N57" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>78</v>
+      </c>
+      <c r="R57" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10981.953125</v>
+        <v>28064.0625</v>
       </c>
       <c r="B58" t="n">
-        <v>465533.515625</v>
+        <v>1184398.1875</v>
       </c>
       <c r="C58" t="n">
-        <v>467.546875</v>
+        <v>1100.09375</v>
       </c>
       <c r="D58" t="n">
-        <v>42</v>
-      </c>
-      <c r="E58" t="inlineStr">
+        <v>5.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>660127050</v>
+      </c>
+      <c r="F58" t="n">
+        <v>431755977</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3205464061</v>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G58" t="n">
-        <v>5.574897766113281</v>
-      </c>
-      <c r="H58" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>44</v>
-      </c>
-      <c r="J58" t="b">
+      <c r="J58" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6.06695556640625</v>
+      </c>
+      <c r="L58" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>78</v>
+      </c>
+      <c r="R58" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10982.296875</v>
+        <v>28064.09375</v>
       </c>
       <c r="B59" t="n">
-        <v>465537.21875</v>
+        <v>1184402.34375</v>
       </c>
       <c r="C59" t="n">
-        <v>467.578125</v>
+        <v>1100.09375</v>
       </c>
       <c r="D59" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>2.6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>660129909</v>
       </c>
       <c r="F59" t="n">
-        <v>15.6518669128418</v>
+        <v>431757699</v>
       </c>
       <c r="G59" t="n">
-        <v>5.677848815917969</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>44</v>
-      </c>
-      <c r="J59" t="b">
+        <v>3205471834</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6.066452026367188</v>
+      </c>
+      <c r="L59" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N59" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>78</v>
+      </c>
+      <c r="R59" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10982.65625</v>
+        <v>28064.140625</v>
       </c>
       <c r="B60" t="n">
-        <v>465540.875</v>
+        <v>1184406.421875</v>
       </c>
       <c r="C60" t="n">
-        <v>467.578125</v>
+        <v>1100.09375</v>
       </c>
       <c r="D60" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E60" t="inlineStr">
+        <v>3.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>660132697</v>
+      </c>
+      <c r="F60" t="n">
+        <v>431759274</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3205480463</v>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G60" t="n">
-        <v>5.671566009521484</v>
-      </c>
-      <c r="H60" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="I60" t="n">
-        <v>44</v>
-      </c>
-      <c r="J60" t="b">
+      <c r="J60" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K60" t="n">
+        <v>6.068023681640625</v>
+      </c>
+      <c r="L60" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>78</v>
+      </c>
+      <c r="R60" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10983.328125</v>
+        <v>28064.15625</v>
       </c>
       <c r="B61" t="n">
-        <v>465544.28125</v>
+        <v>1184410.578125</v>
       </c>
       <c r="C61" t="n">
-        <v>467.578125</v>
+        <v>1100.09375</v>
       </c>
       <c r="D61" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>660135326</v>
       </c>
       <c r="F61" t="n">
-        <v>15.6518669128418</v>
+        <v>431760845</v>
       </c>
       <c r="G61" t="n">
-        <v>5.654994964599609</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="I61" t="n">
-        <v>44</v>
-      </c>
-      <c r="J61" t="b">
+        <v>3205488128</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K61" t="n">
+        <v>6.066562652587891</v>
+      </c>
+      <c r="L61" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N61" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>78</v>
+      </c>
+      <c r="R61" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10983.5625</v>
+        <v>28064.1875</v>
       </c>
       <c r="B62" t="n">
-        <v>465548.15625</v>
+        <v>1184414.734375</v>
       </c>
       <c r="C62" t="n">
-        <v>467.578125</v>
+        <v>1100.09375</v>
       </c>
       <c r="D62" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
-        </is>
+        <v>2.6</v>
+      </c>
+      <c r="E62" t="n">
+        <v>660139218</v>
       </c>
       <c r="F62" t="n">
-        <v>15.6518669128418</v>
+        <v>431762629</v>
       </c>
       <c r="G62" t="n">
-        <v>5.665546417236328</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="I62" t="n">
-        <v>44</v>
-      </c>
-      <c r="J62" t="b">
+        <v>3205500713</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6.069007873535156</v>
+      </c>
+      <c r="L62" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>78</v>
+      </c>
+      <c r="R62" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10983.65625</v>
+        <v>28064.265625</v>
       </c>
       <c r="B63" t="n">
-        <v>465552.046875</v>
+        <v>1184418.984375</v>
       </c>
       <c r="C63" t="n">
-        <v>467.578125</v>
+        <v>1100.09375</v>
       </c>
       <c r="D63" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E63" t="inlineStr">
+        <v>3.2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>660141531</v>
+      </c>
+      <c r="F63" t="n">
+        <v>431763851</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3205506697</v>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G63" t="n">
-        <v>5.671684265136719</v>
-      </c>
-      <c r="H63" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="I63" t="n">
-        <v>44</v>
-      </c>
-      <c r="J63" t="b">
+      <c r="J63" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K63" t="n">
+        <v>6.066638946533203</v>
+      </c>
+      <c r="L63" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>78</v>
+      </c>
+      <c r="R63" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10983.71875</v>
+        <v>28064.28125</v>
       </c>
       <c r="B64" t="n">
-        <v>465556.09375</v>
+        <v>1184423.15625</v>
       </c>
       <c r="C64" t="n">
-        <v>467.578125</v>
+        <v>1100.09375</v>
       </c>
       <c r="D64" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E64" t="inlineStr">
+        <v>1.1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>660143528</v>
+      </c>
+      <c r="F64" t="n">
+        <v>431765024</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3205512596</v>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G64" t="n">
-        <v>5.682685852050781</v>
-      </c>
-      <c r="H64" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="I64" t="n">
-        <v>44</v>
-      </c>
-      <c r="J64" t="b">
+      <c r="J64" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K64" t="n">
+        <v>6.068599700927734</v>
+      </c>
+      <c r="L64" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N64" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>78</v>
+      </c>
+      <c r="R64" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10983.734375</v>
+        <v>28064.359375</v>
       </c>
       <c r="B65" t="n">
-        <v>465560.03125</v>
+        <v>1184427.28125</v>
       </c>
       <c r="C65" t="n">
-        <v>467.59375</v>
+        <v>1100.09375</v>
       </c>
       <c r="D65" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E65" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>660146724</v>
+      </c>
+      <c r="F65" t="n">
+        <v>431766896</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3205524811</v>
+      </c>
+      <c r="I65" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G65" t="n">
-        <v>5.690288543701172</v>
-      </c>
-      <c r="H65" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="I65" t="n">
-        <v>44</v>
-      </c>
-      <c r="J65" t="b">
+      <c r="J65" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K65" t="n">
+        <v>6.068092346191406</v>
+      </c>
+      <c r="L65" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N65" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>78</v>
+      </c>
+      <c r="R65" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>10983.8125</v>
+        <v>28064.46875</v>
       </c>
       <c r="B66" t="n">
-        <v>465564.03125</v>
+        <v>1184431.375</v>
       </c>
       <c r="C66" t="n">
-        <v>467.59375</v>
+        <v>1100.109375</v>
       </c>
       <c r="D66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E66" t="inlineStr">
+        <v>5.1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>660149401</v>
+      </c>
+      <c r="F66" t="n">
+        <v>431768415</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3205535427</v>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G66" t="n">
-        <v>5.701484680175781</v>
-      </c>
-      <c r="H66" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="I66" t="n">
-        <v>44</v>
-      </c>
-      <c r="J66" t="b">
+      <c r="J66" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K66" t="n">
+        <v>6.068332672119141</v>
+      </c>
+      <c r="L66" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N66" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>78</v>
+      </c>
+      <c r="R66" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10983.875</v>
+        <v>28064.53125</v>
       </c>
       <c r="B67" t="n">
-        <v>465568.015625</v>
+        <v>1184435.421875</v>
       </c>
       <c r="C67" t="n">
-        <v>467.59375</v>
+        <v>1100.109375</v>
       </c>
       <c r="D67" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E67" t="inlineStr">
+        <v>3.7</v>
+      </c>
+      <c r="E67" t="n">
+        <v>660152322</v>
+      </c>
+      <c r="F67" t="n">
+        <v>431770118</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3205544204</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K67" t="n">
+        <v>6.069248199462891</v>
+      </c>
+      <c r="L67" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N67" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>78</v>
+      </c>
+      <c r="R67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>28064.609375</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1184439.53125</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1100.109375</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>660155464</v>
+      </c>
+      <c r="F68" t="n">
+        <v>431771833</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3205554385</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K68" t="n">
+        <v>6.070350646972656</v>
+      </c>
+      <c r="L68" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M68" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N68" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>78</v>
+      </c>
+      <c r="R68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>28064.65625</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1184443.71875</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1100.109375</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>660158421</v>
+      </c>
+      <c r="F69" t="n">
+        <v>431773592</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3205563637</v>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="G67" t="n">
-        <v>5.701698303222656</v>
-      </c>
-      <c r="H67" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="I67" t="n">
-        <v>44</v>
-      </c>
-      <c r="J67" t="b">
+      <c r="J69" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K69" t="n">
+        <v>6.066944122314453</v>
+      </c>
+      <c r="L69" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N69" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>78</v>
+      </c>
+      <c r="R69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>28064.703125</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1184447.703125</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1100.109375</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>660161154</v>
+      </c>
+      <c r="F70" t="n">
+        <v>431775127</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3205572040</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K70" t="n">
+        <v>6.068519592285156</v>
+      </c>
+      <c r="L70" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N70" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>78</v>
+      </c>
+      <c r="R70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>28064.8125</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1184451.859375</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1100.109375</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>660163618</v>
+      </c>
+      <c r="F71" t="n">
+        <v>431776611</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3205579692</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>scpufreq(current=2496.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K71" t="n">
+        <v>6.066864013671875</v>
+      </c>
+      <c r="L71" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N71" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>78</v>
+      </c>
+      <c r="R71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>28064.96875</v>
+      </c>
+      <c r="B72" t="n">
+        <v>1184455.734375</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1100.125</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>660171439</v>
+      </c>
+      <c r="F72" t="n">
+        <v>431780768</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3205610651</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K72" t="n">
+        <v>6.061244964599609</v>
+      </c>
+      <c r="L72" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M72" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N72" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>78</v>
+      </c>
+      <c r="R72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>28065.015625</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1184459.8125</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1100.125</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E73" t="n">
+        <v>660175531</v>
+      </c>
+      <c r="F73" t="n">
+        <v>431783127</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3205624175</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>scpufreq(current=998.0, min=0.0, max=2496.0)</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="K73" t="n">
+        <v>6.055145263671875</v>
+      </c>
+      <c r="L73" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="M73" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N73" t="n">
+        <v>7.416301727294922</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.0836982727050781</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>78</v>
+      </c>
+      <c r="R73" t="b">
         <v>0</v>
       </c>
     </row>

--- a/labelled_dataset.xlsx
+++ b/labelled_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,32 +538,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11:53:13</t>
+          <t>12:08:06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4598.9375</v>
+        <v>4973.46875</v>
       </c>
       <c r="C2" t="n">
-        <v>70989.06249999999</v>
+        <v>77580.203125</v>
       </c>
       <c r="D2" t="n">
-        <v>128.640625</v>
+        <v>136.578125</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="F2" t="n">
-        <v>62868779</v>
+        <v>68836181</v>
       </c>
       <c r="G2" t="n">
-        <v>40513726</v>
+        <v>44250452</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>291995144</v>
+        <v>316025314</v>
       </c>
       <c r="J2" t="n">
         <v>2496</v>
@@ -578,25 +578,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N2" t="n">
-        <v>6.330150604248047</v>
+        <v>6.553558349609375</v>
       </c>
       <c r="O2" t="n">
-        <v>59.6</v>
+        <v>58.1</v>
       </c>
       <c r="P2" t="n">
         <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R2" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S2" t="n">
         <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -605,32 +605,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11:53:15</t>
+          <t>12:08:07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4599.125</v>
+        <v>4973.921875</v>
       </c>
       <c r="C3" t="n">
-        <v>71000.20312499999</v>
+        <v>77590.15625</v>
       </c>
       <c r="D3" t="n">
-        <v>128.640625</v>
+        <v>136.578125</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="F3" t="n">
-        <v>62876258</v>
+        <v>68855543</v>
       </c>
       <c r="G3" t="n">
-        <v>40518169</v>
+        <v>44261290</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>292078381</v>
+        <v>316161480</v>
       </c>
       <c r="J3" t="n">
         <v>2496</v>
@@ -645,25 +645,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N3" t="n">
-        <v>6.328075408935547</v>
+        <v>6.542434692382812</v>
       </c>
       <c r="O3" t="n">
-        <v>59.6</v>
+        <v>58.2</v>
       </c>
       <c r="P3" t="n">
         <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S3" t="n">
         <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -672,32 +672,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:53:16</t>
+          <t>12:08:08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4599.328125</v>
+        <v>4974.234375</v>
       </c>
       <c r="C4" t="n">
-        <v>71007.82812499999</v>
+        <v>77597.859375</v>
       </c>
       <c r="D4" t="n">
-        <v>128.640625</v>
+        <v>136.578125</v>
       </c>
       <c r="E4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F4" t="n">
-        <v>62891898</v>
+        <v>68873424</v>
       </c>
       <c r="G4" t="n">
-        <v>40526967</v>
+        <v>44271705</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>292149342</v>
+        <v>316237273</v>
       </c>
       <c r="J4" t="n">
         <v>2496</v>
@@ -712,25 +712,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N4" t="n">
-        <v>6.326259613037109</v>
+        <v>6.539337158203125</v>
       </c>
       <c r="O4" t="n">
-        <v>59.6</v>
+        <v>58.2</v>
       </c>
       <c r="P4" t="n">
         <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S4" t="n">
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -739,32 +739,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11:53:17</t>
+          <t>12:08:09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4599.859375</v>
+        <v>4974.40625</v>
       </c>
       <c r="C5" t="n">
-        <v>71015.26562499999</v>
+        <v>77605.703125</v>
       </c>
       <c r="D5" t="n">
-        <v>128.640625</v>
+        <v>136.578125</v>
       </c>
       <c r="E5" t="n">
-        <v>9.9</v>
+        <v>4.6</v>
       </c>
       <c r="F5" t="n">
-        <v>62909525</v>
+        <v>68881405</v>
       </c>
       <c r="G5" t="n">
-        <v>40536933</v>
+        <v>44276803</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>292222307</v>
+        <v>316255924</v>
       </c>
       <c r="J5" t="n">
         <v>2496</v>
@@ -779,25 +779,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N5" t="n">
-        <v>6.327285766601562</v>
+        <v>6.541553497314453</v>
       </c>
       <c r="O5" t="n">
-        <v>59.6</v>
+        <v>58.2</v>
       </c>
       <c r="P5" t="n">
         <v>7.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S5" t="n">
         <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -806,32 +806,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11:53:18</t>
+          <t>12:08:10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4600.109375</v>
+        <v>4974.65625</v>
       </c>
       <c r="C6" t="n">
-        <v>71022.93749999999</v>
+        <v>77613.421875</v>
       </c>
       <c r="D6" t="n">
-        <v>128.640625</v>
+        <v>136.578125</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="F6" t="n">
-        <v>62920198</v>
+        <v>68890400</v>
       </c>
       <c r="G6" t="n">
-        <v>40543199</v>
+        <v>44281982</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>292249127</v>
+        <v>316283610</v>
       </c>
       <c r="J6" t="n">
         <v>2496</v>
@@ -846,25 +846,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N6" t="n">
-        <v>6.3309326171875</v>
+        <v>6.551536560058594</v>
       </c>
       <c r="O6" t="n">
-        <v>59.6</v>
+        <v>58.1</v>
       </c>
       <c r="P6" t="n">
         <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S6" t="n">
         <v>1.2</v>
       </c>
       <c r="T6" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -873,35 +873,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11:53:19</t>
+          <t>12:08:11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4600.1875</v>
+        <v>4975.015625</v>
       </c>
       <c r="C7" t="n">
-        <v>71030.79687499999</v>
+        <v>77621.125</v>
       </c>
       <c r="D7" t="n">
-        <v>128.65625</v>
+        <v>136.59375</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="F7" t="n">
-        <v>62932331</v>
+        <v>68906666</v>
       </c>
       <c r="G7" t="n">
-        <v>40550394</v>
+        <v>44291176</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>292283846</v>
+        <v>316340475</v>
       </c>
       <c r="J7" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -913,25 +913,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N7" t="n">
-        <v>6.327335357666016</v>
+        <v>6.533096313476562</v>
       </c>
       <c r="O7" t="n">
-        <v>59.6</v>
+        <v>58.3</v>
       </c>
       <c r="P7" t="n">
         <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S7" t="n">
         <v>1.2</v>
       </c>
       <c r="T7" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -940,35 +940,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11:53:20</t>
+          <t>12:08:12</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4600.296875</v>
+        <v>4975.1875</v>
       </c>
       <c r="C8" t="n">
-        <v>71038.59374999999</v>
+        <v>77628.921875</v>
       </c>
       <c r="D8" t="n">
-        <v>128.671875</v>
+        <v>136.59375</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="F8" t="n">
-        <v>62937222</v>
+        <v>68920089</v>
       </c>
       <c r="G8" t="n">
-        <v>40553189</v>
+        <v>44298997</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>292301563</v>
+        <v>316385674</v>
       </c>
       <c r="J8" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -980,25 +980,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N8" t="n">
-        <v>6.328464508056641</v>
+        <v>6.539230346679688</v>
       </c>
       <c r="O8" t="n">
-        <v>59.6</v>
+        <v>58.2</v>
       </c>
       <c r="P8" t="n">
         <v>7.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1007,35 +1007,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11:53:21</t>
+          <t>12:08:13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4600.53125</v>
+        <v>4975.4375</v>
       </c>
       <c r="C9" t="n">
-        <v>71046.39062499999</v>
+        <v>77636.390625</v>
       </c>
       <c r="D9" t="n">
-        <v>128.71875</v>
+        <v>136.625</v>
       </c>
       <c r="E9" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="F9" t="n">
-        <v>62949062</v>
+        <v>68935709</v>
       </c>
       <c r="G9" t="n">
-        <v>40560104</v>
+        <v>44308019</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>292371567</v>
+        <v>316460897</v>
       </c>
       <c r="J9" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1047,25 +1047,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N9" t="n">
-        <v>6.334060668945312</v>
+        <v>6.540241241455078</v>
       </c>
       <c r="O9" t="n">
-        <v>59.5</v>
+        <v>58.2</v>
       </c>
       <c r="P9" t="n">
         <v>7.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S9" t="n">
         <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1074,32 +1074,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11:53:22</t>
+          <t>12:08:14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4600.84375</v>
+        <v>4975.515625</v>
       </c>
       <c r="C10" t="n">
-        <v>71054.06249999999</v>
+        <v>77644.296875</v>
       </c>
       <c r="D10" t="n">
-        <v>128.71875</v>
+        <v>136.640625</v>
       </c>
       <c r="E10" t="n">
-        <v>6.7</v>
+        <v>4.7</v>
       </c>
       <c r="F10" t="n">
-        <v>62965423</v>
+        <v>68948617</v>
       </c>
       <c r="G10" t="n">
-        <v>40569220</v>
+        <v>44315498</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>292439587</v>
+        <v>316494145</v>
       </c>
       <c r="J10" t="n">
         <v>2496</v>
@@ -1114,25 +1114,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N10" t="n">
-        <v>6.313079833984375</v>
+        <v>6.540279388427734</v>
       </c>
       <c r="O10" t="n">
-        <v>59.7</v>
+        <v>58.2</v>
       </c>
       <c r="P10" t="n">
         <v>7.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R10" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S10" t="n">
         <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1141,32 +1141,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11:53:23</t>
+          <t>12:08:15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4601.5625</v>
+        <v>4975.59375</v>
       </c>
       <c r="C11" t="n">
-        <v>71061.20312499999</v>
+        <v>77652.34375</v>
       </c>
       <c r="D11" t="n">
-        <v>128.71875</v>
+        <v>136.640625</v>
       </c>
       <c r="E11" t="n">
-        <v>11.6</v>
+        <v>1.7</v>
       </c>
       <c r="F11" t="n">
-        <v>62977886</v>
+        <v>68956078</v>
       </c>
       <c r="G11" t="n">
-        <v>40576499</v>
+        <v>44319783</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>292474619</v>
+        <v>316512119</v>
       </c>
       <c r="J11" t="n">
         <v>2496</v>
@@ -1181,25 +1181,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N11" t="n">
-        <v>6.324928283691406</v>
+        <v>6.543418884277344</v>
       </c>
       <c r="O11" t="n">
-        <v>59.6</v>
+        <v>58.2</v>
       </c>
       <c r="P11" t="n">
         <v>7.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R11" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S11" t="n">
         <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -1208,32 +1208,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11:53:24</t>
+          <t>12:08:16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4601.90625</v>
+        <v>4975.671875</v>
       </c>
       <c r="C12" t="n">
-        <v>71068.89062499999</v>
+        <v>77660.421875</v>
       </c>
       <c r="D12" t="n">
-        <v>128.734375</v>
+        <v>136.640625</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>62991237</v>
+        <v>68961939</v>
       </c>
       <c r="G12" t="n">
-        <v>40584371</v>
+        <v>44323103</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>292544186</v>
+        <v>316529993</v>
       </c>
       <c r="J12" t="n">
         <v>2496</v>
@@ -1248,25 +1248,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N12" t="n">
-        <v>6.302074432373047</v>
+        <v>6.550701141357422</v>
       </c>
       <c r="O12" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="P12" t="n">
         <v>7.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S12" t="n">
         <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1275,32 +1275,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11:53:25</t>
+          <t>12:08:17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4602.171875</v>
+        <v>4975.75</v>
       </c>
       <c r="C13" t="n">
-        <v>71076.46874999999</v>
+        <v>77668.40625</v>
       </c>
       <c r="D13" t="n">
-        <v>128.734375</v>
+        <v>136.640625</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="F13" t="n">
-        <v>63005510</v>
+        <v>68967253</v>
       </c>
       <c r="G13" t="n">
-        <v>40597856</v>
+        <v>44326228</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>292648360</v>
+        <v>316544995</v>
       </c>
       <c r="J13" t="n">
         <v>2496</v>
@@ -1315,25 +1315,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N13" t="n">
-        <v>6.08929443359375</v>
+        <v>6.548114776611328</v>
       </c>
       <c r="O13" t="n">
-        <v>61.1</v>
+        <v>58.2</v>
       </c>
       <c r="P13" t="n">
         <v>7.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S13" t="n">
         <v>1.2</v>
       </c>
       <c r="T13" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -1342,32 +1342,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11:53:26</t>
+          <t>12:08:18</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4602.53125</v>
+        <v>4976.609375</v>
       </c>
       <c r="C14" t="n">
-        <v>71083.95312499999</v>
+        <v>77675.453125</v>
       </c>
       <c r="D14" t="n">
-        <v>128.75</v>
+        <v>136.65625</v>
       </c>
       <c r="E14" t="n">
-        <v>8.1</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
-        <v>63023581</v>
+        <v>68978479</v>
       </c>
       <c r="G14" t="n">
-        <v>40613595</v>
+        <v>44332848</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>292734468</v>
+        <v>316612220</v>
       </c>
       <c r="J14" t="n">
         <v>2496</v>
@@ -1382,25 +1382,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N14" t="n">
-        <v>5.979202270507812</v>
+        <v>6.554271697998047</v>
       </c>
       <c r="O14" t="n">
-        <v>61.8</v>
+        <v>58.1</v>
       </c>
       <c r="P14" t="n">
         <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R14" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S14" t="n">
         <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -1409,32 +1409,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11:53:27</t>
+          <t>12:08:19</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4602.65625</v>
+        <v>4976.625</v>
       </c>
       <c r="C15" t="n">
-        <v>71091.56249999999</v>
+        <v>77683.53125</v>
       </c>
       <c r="D15" t="n">
-        <v>128.75</v>
+        <v>136.6875</v>
       </c>
       <c r="E15" t="n">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="n">
-        <v>63032492</v>
+        <v>68983436</v>
       </c>
       <c r="G15" t="n">
-        <v>40625164</v>
+        <v>44335756</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>292760500</v>
+        <v>316625712</v>
       </c>
       <c r="J15" t="n">
         <v>2496</v>
@@ -1449,25 +1449,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N15" t="n">
-        <v>5.809249877929688</v>
+        <v>6.556537628173828</v>
       </c>
       <c r="O15" t="n">
-        <v>62.9</v>
+        <v>58.1</v>
       </c>
       <c r="P15" t="n">
         <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R15" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S15" t="n">
         <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
@@ -1476,32 +1476,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11:53:28</t>
+          <t>12:08:20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4602.765625</v>
+        <v>4976.828125</v>
       </c>
       <c r="C16" t="n">
-        <v>71099.12499999999</v>
+        <v>77691.421875</v>
       </c>
       <c r="D16" t="n">
-        <v>128.75</v>
+        <v>136.6875</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="F16" t="n">
-        <v>63039350</v>
+        <v>68992032</v>
       </c>
       <c r="G16" t="n">
-        <v>40638213</v>
+        <v>44340588</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>292781093</v>
+        <v>316653612</v>
       </c>
       <c r="J16" t="n">
         <v>2496</v>
@@ -1516,25 +1516,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N16" t="n">
-        <v>5.621261596679688</v>
+        <v>6.5462646484375</v>
       </c>
       <c r="O16" t="n">
-        <v>64.09999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="P16" t="n">
         <v>7.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R16" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S16" t="n">
         <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -1543,35 +1543,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11:53:29</t>
+          <t>12:08:21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4603.1875</v>
+        <v>4977.109375</v>
       </c>
       <c r="C17" t="n">
-        <v>71106.74999999999</v>
+        <v>77699.0625</v>
       </c>
       <c r="D17" t="n">
-        <v>128.75</v>
+        <v>136.6875</v>
       </c>
       <c r="E17" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="F17" t="n">
-        <v>63044610</v>
+        <v>69008585</v>
       </c>
       <c r="G17" t="n">
-        <v>40641476</v>
+        <v>44350681</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>292807564</v>
+        <v>316792373</v>
       </c>
       <c r="J17" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1583,25 +1583,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N17" t="n">
-        <v>5.432334899902344</v>
+        <v>6.519325256347656</v>
       </c>
       <c r="O17" t="n">
-        <v>65.3</v>
+        <v>58.3</v>
       </c>
       <c r="P17" t="n">
         <v>7.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R17" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S17" t="n">
         <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -1610,32 +1610,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11:53:30</t>
+          <t>12:08:22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4603.265625</v>
+        <v>4977.21875</v>
       </c>
       <c r="C18" t="n">
-        <v>71114.54687499999</v>
+        <v>77707</v>
       </c>
       <c r="D18" t="n">
-        <v>128.765625</v>
+        <v>136.6875</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>63049850</v>
+        <v>69013042</v>
       </c>
       <c r="G18" t="n">
-        <v>40652290</v>
+        <v>44353305</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>292827799</v>
+        <v>316816303</v>
       </c>
       <c r="J18" t="n">
         <v>2496</v>
@@ -1650,25 +1650,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2452392578125</v>
+        <v>6.518100738525391</v>
       </c>
       <c r="O18" t="n">
-        <v>66.5</v>
+        <v>58.4</v>
       </c>
       <c r="P18" t="n">
         <v>7.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R18" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S18" t="n">
         <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
@@ -1677,32 +1677,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11:53:31</t>
+          <t>12:08:23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4603.484375</v>
+        <v>4977.34375</v>
       </c>
       <c r="C19" t="n">
-        <v>71122.12499999999</v>
+        <v>77714.8125</v>
       </c>
       <c r="D19" t="n">
-        <v>128.765625</v>
+        <v>136.6875</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>63065493</v>
+        <v>69022282</v>
       </c>
       <c r="G19" t="n">
-        <v>40661693</v>
+        <v>44358788</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>292908305</v>
+        <v>316877817</v>
       </c>
       <c r="J19" t="n">
         <v>2496</v>
@@ -1717,25 +1717,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N19" t="n">
-        <v>5.039470672607422</v>
+        <v>6.519477844238281</v>
       </c>
       <c r="O19" t="n">
-        <v>67.8</v>
+        <v>58.3</v>
       </c>
       <c r="P19" t="n">
         <v>7.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R19" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S19" t="n">
         <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
@@ -1744,35 +1744,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11:53:32</t>
+          <t>12:08:24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4603.65625</v>
+        <v>4977.40625</v>
       </c>
       <c r="C20" t="n">
-        <v>71129.31249999999</v>
+        <v>77722.75</v>
       </c>
       <c r="D20" t="n">
-        <v>128.78125</v>
+        <v>136.6875</v>
       </c>
       <c r="E20" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="F20" t="n">
-        <v>63073615</v>
+        <v>69026366</v>
       </c>
       <c r="G20" t="n">
-        <v>40666642</v>
+        <v>44361135</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>292931780</v>
+        <v>316893337</v>
       </c>
       <c r="J20" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1784,25 +1784,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9134521484375</v>
+        <v>6.529220581054688</v>
       </c>
       <c r="O20" t="n">
-        <v>68.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="P20" t="n">
         <v>7.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R20" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S20" t="n">
         <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
@@ -1811,32 +1811,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11:53:33</t>
+          <t>12:08:25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4603.71875</v>
+        <v>4977.515625</v>
       </c>
       <c r="C21" t="n">
-        <v>71136.32812499999</v>
+        <v>77730.765625</v>
       </c>
       <c r="D21" t="n">
-        <v>128.796875</v>
+        <v>136.6875</v>
       </c>
       <c r="E21" t="n">
-        <v>14.3</v>
+        <v>3.2</v>
       </c>
       <c r="F21" t="n">
-        <v>63084948</v>
+        <v>69035730</v>
       </c>
       <c r="G21" t="n">
-        <v>40673354</v>
+        <v>44366683</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>292954935</v>
+        <v>316916728</v>
       </c>
       <c r="J21" t="n">
         <v>2496</v>
@@ -1851,25 +1851,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N21" t="n">
-        <v>4.811824798583984</v>
+        <v>6.529335021972656</v>
       </c>
       <c r="O21" t="n">
-        <v>69.3</v>
+        <v>58.3</v>
       </c>
       <c r="P21" t="n">
         <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R21" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S21" t="n">
         <v>1.2</v>
       </c>
       <c r="T21" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U21" t="b">
         <v>0</v>
@@ -1878,32 +1878,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11:53:34</t>
+          <t>12:08:26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4603.765625</v>
+        <v>4977.828125</v>
       </c>
       <c r="C22" t="n">
-        <v>71144.06249999999</v>
+        <v>77738.328125</v>
       </c>
       <c r="D22" t="n">
-        <v>128.796875</v>
+        <v>136.703125</v>
       </c>
       <c r="E22" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="F22" t="n">
-        <v>63091881</v>
+        <v>69046971</v>
       </c>
       <c r="G22" t="n">
-        <v>40677349</v>
+        <v>44373580</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>292980806</v>
+        <v>316947651</v>
       </c>
       <c r="J22" t="n">
         <v>2496</v>
@@ -1918,25 +1918,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N22" t="n">
-        <v>4.717411041259766</v>
+        <v>6.530876159667969</v>
       </c>
       <c r="O22" t="n">
-        <v>69.90000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="P22" t="n">
         <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R22" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S22" t="n">
         <v>1.2</v>
       </c>
       <c r="T22" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
@@ -1945,32 +1945,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11:53:35</t>
+          <t>12:08:27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4603.8125</v>
+        <v>4977.90625</v>
       </c>
       <c r="C23" t="n">
-        <v>71152.01562499999</v>
+        <v>77746.40625</v>
       </c>
       <c r="D23" t="n">
-        <v>128.796875</v>
+        <v>136.71875</v>
       </c>
       <c r="E23" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="F23" t="n">
-        <v>63096650</v>
+        <v>69051931</v>
       </c>
       <c r="G23" t="n">
-        <v>40680174</v>
+        <v>44376632</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>292998399</v>
+        <v>316965846</v>
       </c>
       <c r="J23" t="n">
         <v>2496</v>
@@ -1985,25 +1985,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N23" t="n">
-        <v>4.618400573730469</v>
+        <v>6.532306671142578</v>
       </c>
       <c r="O23" t="n">
-        <v>70.5</v>
+        <v>58.3</v>
       </c>
       <c r="P23" t="n">
         <v>7.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R23" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S23" t="n">
         <v>1.2</v>
       </c>
       <c r="T23" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U23" t="b">
         <v>0</v>
@@ -2012,32 +2012,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11:53:36</t>
+          <t>12:08:28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4604.1875</v>
+        <v>4978.03125</v>
       </c>
       <c r="C24" t="n">
-        <v>71158.56249999999</v>
+        <v>77754.171875</v>
       </c>
       <c r="D24" t="n">
-        <v>128.828125</v>
+        <v>136.71875</v>
       </c>
       <c r="E24" t="n">
-        <v>20.6</v>
+        <v>6.4</v>
       </c>
       <c r="F24" t="n">
-        <v>63111192</v>
+        <v>69062653</v>
       </c>
       <c r="G24" t="n">
-        <v>40690804</v>
+        <v>44382269</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>293074652</v>
+        <v>317034015</v>
       </c>
       <c r="J24" t="n">
         <v>2496</v>
@@ -2052,25 +2052,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N24" t="n">
-        <v>6.492271423339844</v>
+        <v>6.540813446044922</v>
       </c>
       <c r="O24" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="P24" t="n">
         <v>7.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R24" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S24" t="n">
         <v>1.2</v>
       </c>
       <c r="T24" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U24" t="b">
         <v>0</v>
@@ -2079,32 +2079,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11:53:37</t>
+          <t>12:08:29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4604.359375</v>
+        <v>4978.125</v>
       </c>
       <c r="C25" t="n">
-        <v>71166.34374999999</v>
+        <v>77762.125</v>
       </c>
       <c r="D25" t="n">
-        <v>128.828125</v>
+        <v>136.71875</v>
       </c>
       <c r="E25" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="F25" t="n">
-        <v>63122988</v>
+        <v>69066759</v>
       </c>
       <c r="G25" t="n">
-        <v>40697942</v>
+        <v>44384702</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>293111352</v>
+        <v>317046674</v>
       </c>
       <c r="J25" t="n">
         <v>998</v>
@@ -2119,25 +2119,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N25" t="n">
-        <v>6.488651275634766</v>
+        <v>6.54339599609375</v>
       </c>
       <c r="O25" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="P25" t="n">
         <v>7.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R25" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S25" t="n">
         <v>1.2</v>
       </c>
       <c r="T25" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -2146,32 +2146,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11:53:38</t>
+          <t>12:08:30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4604.515625</v>
+        <v>4978.40625</v>
       </c>
       <c r="C26" t="n">
-        <v>71174.15624999999</v>
+        <v>77769.875</v>
       </c>
       <c r="D26" t="n">
-        <v>128.828125</v>
+        <v>136.71875</v>
       </c>
       <c r="E26" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="F26" t="n">
-        <v>63128563</v>
+        <v>69072540</v>
       </c>
       <c r="G26" t="n">
-        <v>40701159</v>
+        <v>44388187</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>293128895</v>
+        <v>317065998</v>
       </c>
       <c r="J26" t="n">
         <v>2496</v>
@@ -2186,25 +2186,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N26" t="n">
-        <v>6.486068725585938</v>
+        <v>6.548435211181641</v>
       </c>
       <c r="O26" t="n">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="P26" t="n">
         <v>7.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R26" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S26" t="n">
         <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U26" t="b">
         <v>0</v>
@@ -2213,32 +2213,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11:53:39</t>
+          <t>12:08:31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4604.609375</v>
+        <v>4978.46875</v>
       </c>
       <c r="C27" t="n">
-        <v>71182.14062499999</v>
+        <v>77777.890625</v>
       </c>
       <c r="D27" t="n">
-        <v>128.828125</v>
+        <v>136.71875</v>
       </c>
       <c r="E27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F27" t="n">
-        <v>63132657</v>
+        <v>69076257</v>
       </c>
       <c r="G27" t="n">
-        <v>40703477</v>
+        <v>44390431</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>293145536</v>
+        <v>317079993</v>
       </c>
       <c r="J27" t="n">
         <v>2496</v>
@@ -2253,25 +2253,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N27" t="n">
-        <v>6.484058380126953</v>
+        <v>6.548500061035156</v>
       </c>
       <c r="O27" t="n">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="P27" t="n">
         <v>7.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R27" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S27" t="n">
         <v>1.2</v>
       </c>
       <c r="T27" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
@@ -2280,32 +2280,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11:53:40</t>
+          <t>12:08:33</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4604.84375</v>
+        <v>4978.53125</v>
       </c>
       <c r="C28" t="n">
-        <v>71189.95312499999</v>
+        <v>77785.703125</v>
       </c>
       <c r="D28" t="n">
-        <v>128.84375</v>
+        <v>136.71875</v>
       </c>
       <c r="E28" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="F28" t="n">
-        <v>63140499</v>
+        <v>69080127</v>
       </c>
       <c r="G28" t="n">
-        <v>40708710</v>
+        <v>44392709</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>293169011</v>
+        <v>317097320</v>
       </c>
       <c r="J28" t="n">
         <v>2496</v>
@@ -2320,25 +2320,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N28" t="n">
-        <v>6.4842529296875</v>
+        <v>6.545921325683594</v>
       </c>
       <c r="O28" t="n">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="P28" t="n">
         <v>7.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R28" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S28" t="n">
         <v>1.2</v>
       </c>
       <c r="T28" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U28" t="b">
         <v>0</v>
@@ -2347,35 +2347,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11:53:41</t>
+          <t>12:08:34</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4605.109375</v>
+        <v>4978.703125</v>
       </c>
       <c r="C29" t="n">
-        <v>71197.59374999999</v>
+        <v>77793.578125</v>
       </c>
       <c r="D29" t="n">
-        <v>128.859375</v>
+        <v>136.71875</v>
       </c>
       <c r="E29" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>63155518</v>
+        <v>69089276</v>
       </c>
       <c r="G29" t="n">
-        <v>40717726</v>
+        <v>44398057</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>293252466</v>
+        <v>317159458</v>
       </c>
       <c r="J29" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2387,25 +2387,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N29" t="n">
-        <v>6.453620910644531</v>
+        <v>6.537578582763672</v>
       </c>
       <c r="O29" t="n">
-        <v>58.8</v>
+        <v>58.2</v>
       </c>
       <c r="P29" t="n">
         <v>7.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R29" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S29" t="n">
         <v>1.2</v>
       </c>
       <c r="T29" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U29" t="b">
         <v>0</v>
@@ -2414,32 +2414,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11:53:42</t>
+          <t>12:08:35</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4605.28125</v>
+        <v>4978.828125</v>
       </c>
       <c r="C30" t="n">
-        <v>71205.24999999999</v>
+        <v>77801.484375</v>
       </c>
       <c r="D30" t="n">
-        <v>128.859375</v>
+        <v>136.71875</v>
       </c>
       <c r="E30" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="F30" t="n">
-        <v>63165777</v>
+        <v>69093564</v>
       </c>
       <c r="G30" t="n">
-        <v>40723895</v>
+        <v>44400594</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>293290368</v>
+        <v>317175025</v>
       </c>
       <c r="J30" t="n">
         <v>2496</v>
@@ -2454,25 +2454,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N30" t="n">
-        <v>6.484733581542969</v>
+        <v>6.550872802734375</v>
       </c>
       <c r="O30" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="P30" t="n">
         <v>7.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R30" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S30" t="n">
         <v>1.2</v>
       </c>
       <c r="T30" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U30" t="b">
         <v>0</v>
@@ -2481,32 +2481,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11:53:43</t>
+          <t>12:08:36</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4605.609375</v>
+        <v>4978.875</v>
       </c>
       <c r="C31" t="n">
-        <v>71212.90624999999</v>
+        <v>77809.453125</v>
       </c>
       <c r="D31" t="n">
-        <v>128.875</v>
+        <v>136.734375</v>
       </c>
       <c r="E31" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="F31" t="n">
-        <v>63174888</v>
+        <v>69098125</v>
       </c>
       <c r="G31" t="n">
-        <v>40729101</v>
+        <v>44403312</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>293315689</v>
+        <v>317190814</v>
       </c>
       <c r="J31" t="n">
         <v>2496</v>
@@ -2521,25 +2521,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N31" t="n">
-        <v>6.491794586181641</v>
+        <v>6.5517578125</v>
       </c>
       <c r="O31" t="n">
-        <v>58.5</v>
+        <v>58.1</v>
       </c>
       <c r="P31" t="n">
         <v>7.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R31" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S31" t="n">
         <v>1.2</v>
       </c>
       <c r="T31" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U31" t="b">
         <v>0</v>
@@ -2548,35 +2548,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11:53:44</t>
+          <t>12:08:37</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4605.640625</v>
+        <v>4979.03125</v>
       </c>
       <c r="C32" t="n">
-        <v>71220.85937499999</v>
+        <v>77817.265625</v>
       </c>
       <c r="D32" t="n">
-        <v>128.875</v>
+        <v>136.75</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="F32" t="n">
-        <v>63182397</v>
+        <v>69103657</v>
       </c>
       <c r="G32" t="n">
-        <v>40733547</v>
+        <v>44406342</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>293339610</v>
+        <v>317213429</v>
       </c>
       <c r="J32" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2588,25 +2588,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N32" t="n">
-        <v>6.494270324707031</v>
+        <v>6.552387237548828</v>
       </c>
       <c r="O32" t="n">
-        <v>58.5</v>
+        <v>58.1</v>
       </c>
       <c r="P32" t="n">
         <v>7.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R32" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S32" t="n">
         <v>1.2</v>
       </c>
       <c r="T32" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U32" t="b">
         <v>0</v>
@@ -2615,32 +2615,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11:53:45</t>
+          <t>12:08:38</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4605.8125</v>
+        <v>4979.125</v>
       </c>
       <c r="C33" t="n">
-        <v>71228.56249999999</v>
+        <v>77825.234375</v>
       </c>
       <c r="D33" t="n">
-        <v>128.890625</v>
+        <v>136.75</v>
       </c>
       <c r="E33" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="F33" t="n">
-        <v>63191153</v>
+        <v>69111462</v>
       </c>
       <c r="G33" t="n">
-        <v>40738771</v>
+        <v>44411005</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>293366840</v>
+        <v>317236593</v>
       </c>
       <c r="J33" t="n">
         <v>2496</v>
@@ -2655,27 +2655,362 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N33" t="n">
-        <v>6.505241394042969</v>
+        <v>6.543037414550781</v>
       </c>
       <c r="O33" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
       <c r="P33" t="n">
         <v>7.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.410758972167969</v>
+        <v>7.407970428466797</v>
       </c>
       <c r="R33" t="n">
-        <v>0.08924102783203119</v>
+        <v>0.0920295715332031</v>
       </c>
       <c r="S33" t="n">
         <v>1.2</v>
       </c>
       <c r="T33" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12:08:39</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4979.40625</v>
+      </c>
+      <c r="C34" t="n">
+        <v>77832.84375</v>
+      </c>
+      <c r="D34" t="n">
+        <v>136.78125</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>69125699</v>
+      </c>
+      <c r="G34" t="n">
+        <v>44419268</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>317311863</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M34" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6.539463043212891</v>
+      </c>
+      <c r="O34" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7.407970428466797</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.0920295715332031</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>77</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12:08:40</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4979.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>77840.6875</v>
+      </c>
+      <c r="D35" t="n">
+        <v>136.796875</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>69133986</v>
+      </c>
+      <c r="G35" t="n">
+        <v>44424125</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>317333319</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M35" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.538005828857422</v>
+      </c>
+      <c r="O35" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7.407970428466797</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.0920295715332031</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>77</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12:08:41</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4979.609375</v>
+      </c>
+      <c r="C36" t="n">
+        <v>77848.734375</v>
+      </c>
+      <c r="D36" t="n">
+        <v>136.796875</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>69144192</v>
+      </c>
+      <c r="G36" t="n">
+        <v>44430673</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>317357609</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M36" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6.537513732910156</v>
+      </c>
+      <c r="O36" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7.407970428466797</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.0920295715332031</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>77</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12:08:42</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4979.734375</v>
+      </c>
+      <c r="C37" t="n">
+        <v>77856.59375</v>
+      </c>
+      <c r="D37" t="n">
+        <v>136.796875</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>69149132</v>
+      </c>
+      <c r="G37" t="n">
+        <v>44433560</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>317382571</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M37" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6.537467956542969</v>
+      </c>
+      <c r="O37" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7.407970428466797</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.0920295715332031</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>77</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12:08:43</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4979.78125</v>
+      </c>
+      <c r="C38" t="n">
+        <v>77864.625</v>
+      </c>
+      <c r="D38" t="n">
+        <v>136.796875</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>69152418</v>
+      </c>
+      <c r="G38" t="n">
+        <v>44435514</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>317394379</v>
+      </c>
+      <c r="J38" t="n">
+        <v>998</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M38" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N38" t="n">
+        <v>6.538341522216797</v>
+      </c>
+      <c r="O38" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>7.407970428466797</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.0920295715332031</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>77</v>
+      </c>
+      <c r="U38" t="b">
         <v>0</v>
       </c>
     </row>

--- a/labelled_dataset.xlsx
+++ b/labelled_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,32 +538,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12:08:06</t>
+          <t>12:21:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4973.46875</v>
+        <v>5090.109375</v>
       </c>
       <c r="C2" t="n">
-        <v>77580.203125</v>
+        <v>83533.6875</v>
       </c>
       <c r="D2" t="n">
-        <v>136.578125</v>
+        <v>143.390625</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>68836181</v>
+        <v>73642628</v>
       </c>
       <c r="G2" t="n">
-        <v>44250452</v>
+        <v>47131167</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>316025314</v>
+        <v>334708894</v>
       </c>
       <c r="J2" t="n">
         <v>2496</v>
@@ -578,25 +578,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N2" t="n">
-        <v>6.553558349609375</v>
+        <v>8.051792144775391</v>
       </c>
       <c r="O2" t="n">
-        <v>58.1</v>
+        <v>48.6</v>
       </c>
       <c r="P2" t="n">
         <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T2" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -605,32 +605,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12:08:07</t>
+          <t>12:21:02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4973.921875</v>
+        <v>5090.234375</v>
       </c>
       <c r="C3" t="n">
-        <v>77590.15625</v>
+        <v>83544.09375</v>
       </c>
       <c r="D3" t="n">
-        <v>136.578125</v>
+        <v>143.390625</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
       <c r="F3" t="n">
-        <v>68855543</v>
+        <v>73652750</v>
       </c>
       <c r="G3" t="n">
-        <v>44261290</v>
+        <v>47137158</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>316161480</v>
+        <v>334793201</v>
       </c>
       <c r="J3" t="n">
         <v>2496</v>
@@ -645,25 +645,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N3" t="n">
-        <v>6.542434692382812</v>
+        <v>8.051074981689453</v>
       </c>
       <c r="O3" t="n">
-        <v>58.2</v>
+        <v>48.6</v>
       </c>
       <c r="P3" t="n">
         <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -672,32 +672,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12:08:08</t>
+          <t>12:21:03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4974.234375</v>
+        <v>5090.5</v>
       </c>
       <c r="C4" t="n">
-        <v>77597.859375</v>
+        <v>83551.765625</v>
       </c>
       <c r="D4" t="n">
-        <v>136.578125</v>
+        <v>143.421875</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="F4" t="n">
-        <v>68873424</v>
+        <v>73669042</v>
       </c>
       <c r="G4" t="n">
-        <v>44271705</v>
+        <v>47146808</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>316237273</v>
+        <v>334864644</v>
       </c>
       <c r="J4" t="n">
         <v>2496</v>
@@ -712,25 +712,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N4" t="n">
-        <v>6.539337158203125</v>
+        <v>8.026874542236328</v>
       </c>
       <c r="O4" t="n">
-        <v>58.2</v>
+        <v>48.7</v>
       </c>
       <c r="P4" t="n">
         <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -739,32 +739,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:08:09</t>
+          <t>12:21:04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4974.40625</v>
+        <v>5090.71875</v>
       </c>
       <c r="C5" t="n">
-        <v>77605.703125</v>
+        <v>83559.453125</v>
       </c>
       <c r="D5" t="n">
-        <v>136.578125</v>
+        <v>143.4375</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="F5" t="n">
-        <v>68881405</v>
+        <v>73683378</v>
       </c>
       <c r="G5" t="n">
-        <v>44276803</v>
+        <v>47154739</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>316255924</v>
+        <v>334928806</v>
       </c>
       <c r="J5" t="n">
         <v>2496</v>
@@ -779,25 +779,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N5" t="n">
-        <v>6.541553497314453</v>
+        <v>8.020225524902344</v>
       </c>
       <c r="O5" t="n">
-        <v>58.2</v>
+        <v>48.8</v>
       </c>
       <c r="P5" t="n">
         <v>7.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -806,32 +806,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:08:10</t>
+          <t>12:21:05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4974.65625</v>
+        <v>5091.140625</v>
       </c>
       <c r="C6" t="n">
-        <v>77613.421875</v>
+        <v>83567.21875</v>
       </c>
       <c r="D6" t="n">
-        <v>136.578125</v>
+        <v>143.4375</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>68890400</v>
+        <v>73695202</v>
       </c>
       <c r="G6" t="n">
-        <v>44281982</v>
+        <v>47161549</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>316283610</v>
+        <v>334960811</v>
       </c>
       <c r="J6" t="n">
         <v>2496</v>
@@ -846,25 +846,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N6" t="n">
-        <v>6.551536560058594</v>
+        <v>8.015823364257812</v>
       </c>
       <c r="O6" t="n">
-        <v>58.1</v>
+        <v>48.8</v>
       </c>
       <c r="P6" t="n">
         <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -873,35 +873,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12:08:11</t>
+          <t>12:21:06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4975.015625</v>
+        <v>5091.421875</v>
       </c>
       <c r="C7" t="n">
-        <v>77621.125</v>
+        <v>83574.765625</v>
       </c>
       <c r="D7" t="n">
-        <v>136.59375</v>
+        <v>143.4375</v>
       </c>
       <c r="E7" t="n">
         <v>6.6</v>
       </c>
       <c r="F7" t="n">
-        <v>68906666</v>
+        <v>73710484</v>
       </c>
       <c r="G7" t="n">
-        <v>44291176</v>
+        <v>47170251</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>316340475</v>
+        <v>335022703</v>
       </c>
       <c r="J7" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -913,25 +913,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N7" t="n">
-        <v>6.533096313476562</v>
+        <v>8.014659881591797</v>
       </c>
       <c r="O7" t="n">
-        <v>58.3</v>
+        <v>48.8</v>
       </c>
       <c r="P7" t="n">
         <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T7" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -940,35 +940,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12:08:12</t>
+          <t>12:21:07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4975.1875</v>
+        <v>5091.515625</v>
       </c>
       <c r="C8" t="n">
-        <v>77628.921875</v>
+        <v>83582.625</v>
       </c>
       <c r="D8" t="n">
-        <v>136.59375</v>
+        <v>143.4375</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="F8" t="n">
-        <v>68920089</v>
+        <v>73719120</v>
       </c>
       <c r="G8" t="n">
-        <v>44298997</v>
+        <v>47175298</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>316385674</v>
+        <v>335043192</v>
       </c>
       <c r="J8" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -980,25 +980,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N8" t="n">
-        <v>6.539230346679688</v>
+        <v>8.017959594726562</v>
       </c>
       <c r="O8" t="n">
-        <v>58.2</v>
+        <v>48.8</v>
       </c>
       <c r="P8" t="n">
         <v>7.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1007,32 +1007,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12:08:13</t>
+          <t>12:21:08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4975.4375</v>
+        <v>5091.6875</v>
       </c>
       <c r="C9" t="n">
-        <v>77636.390625</v>
+        <v>83590.34375</v>
       </c>
       <c r="D9" t="n">
-        <v>136.625</v>
+        <v>143.453125</v>
       </c>
       <c r="E9" t="n">
-        <v>7.9</v>
+        <v>5.4</v>
       </c>
       <c r="F9" t="n">
-        <v>68935709</v>
+        <v>73730571</v>
       </c>
       <c r="G9" t="n">
-        <v>44308019</v>
+        <v>47181951</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>316460897</v>
+        <v>335110605</v>
       </c>
       <c r="J9" t="n">
         <v>2496</v>
@@ -1047,25 +1047,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N9" t="n">
-        <v>6.540241241455078</v>
+        <v>8.025188446044922</v>
       </c>
       <c r="O9" t="n">
-        <v>58.2</v>
+        <v>48.7</v>
       </c>
       <c r="P9" t="n">
         <v>7.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T9" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1074,32 +1074,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12:08:14</t>
+          <t>12:21:09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4975.515625</v>
+        <v>5091.84375</v>
       </c>
       <c r="C10" t="n">
-        <v>77644.296875</v>
+        <v>83598</v>
       </c>
       <c r="D10" t="n">
-        <v>136.640625</v>
+        <v>143.484375</v>
       </c>
       <c r="E10" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="F10" t="n">
-        <v>68948617</v>
+        <v>73741889</v>
       </c>
       <c r="G10" t="n">
-        <v>44315498</v>
+        <v>47188125</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>316494145</v>
+        <v>335204301</v>
       </c>
       <c r="J10" t="n">
         <v>2496</v>
@@ -1114,25 +1114,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N10" t="n">
-        <v>6.540279388427734</v>
+        <v>8.026618957519531</v>
       </c>
       <c r="O10" t="n">
-        <v>58.2</v>
+        <v>48.7</v>
       </c>
       <c r="P10" t="n">
         <v>7.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T10" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1141,32 +1141,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12:08:15</t>
+          <t>12:21:10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4975.59375</v>
+        <v>5091.9375</v>
       </c>
       <c r="C11" t="n">
-        <v>77652.34375</v>
+        <v>83605.96875</v>
       </c>
       <c r="D11" t="n">
-        <v>136.640625</v>
+        <v>143.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="F11" t="n">
-        <v>68956078</v>
+        <v>73747637</v>
       </c>
       <c r="G11" t="n">
-        <v>44319783</v>
+        <v>47191667</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>316512119</v>
+        <v>335220062</v>
       </c>
       <c r="J11" t="n">
         <v>2496</v>
@@ -1181,25 +1181,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N11" t="n">
-        <v>6.543418884277344</v>
+        <v>8.026691436767578</v>
       </c>
       <c r="O11" t="n">
-        <v>58.2</v>
+        <v>48.7</v>
       </c>
       <c r="P11" t="n">
         <v>7.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T11" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -1208,35 +1208,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12:08:16</t>
+          <t>12:21:11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4975.671875</v>
+        <v>5092.078125</v>
       </c>
       <c r="C12" t="n">
-        <v>77660.421875</v>
+        <v>83613.890625</v>
       </c>
       <c r="D12" t="n">
-        <v>136.640625</v>
+        <v>143.5</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F12" t="n">
-        <v>68961939</v>
+        <v>73753570</v>
       </c>
       <c r="G12" t="n">
-        <v>44323103</v>
+        <v>47195033</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>316529993</v>
+        <v>335238531</v>
       </c>
       <c r="J12" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1248,25 +1248,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N12" t="n">
-        <v>6.550701141357422</v>
+        <v>8.023761749267578</v>
       </c>
       <c r="O12" t="n">
-        <v>58.1</v>
+        <v>48.7</v>
       </c>
       <c r="P12" t="n">
         <v>7.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T12" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1275,32 +1275,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12:08:17</t>
+          <t>12:21:12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4975.75</v>
+        <v>5092.078125</v>
       </c>
       <c r="C13" t="n">
-        <v>77668.40625</v>
+        <v>83621.9375</v>
       </c>
       <c r="D13" t="n">
-        <v>136.640625</v>
+        <v>143.5</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="n">
-        <v>68967253</v>
+        <v>73758318</v>
       </c>
       <c r="G13" t="n">
-        <v>44326228</v>
+        <v>47197804</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>316544995</v>
+        <v>335248803</v>
       </c>
       <c r="J13" t="n">
         <v>2496</v>
@@ -1315,25 +1315,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N13" t="n">
-        <v>6.548114776611328</v>
+        <v>8.025440216064453</v>
       </c>
       <c r="O13" t="n">
-        <v>58.2</v>
+        <v>48.7</v>
       </c>
       <c r="P13" t="n">
         <v>7.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T13" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -1342,32 +1342,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12:08:18</t>
+          <t>12:21:13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4976.609375</v>
+        <v>5092.265625</v>
       </c>
       <c r="C14" t="n">
-        <v>77675.453125</v>
+        <v>83629.75</v>
       </c>
       <c r="D14" t="n">
-        <v>136.65625</v>
+        <v>143.5</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8</v>
+        <v>4.2</v>
       </c>
       <c r="F14" t="n">
-        <v>68978479</v>
+        <v>73769713</v>
       </c>
       <c r="G14" t="n">
-        <v>44332848</v>
+        <v>47204298</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>316612220</v>
+        <v>335317048</v>
       </c>
       <c r="J14" t="n">
         <v>2496</v>
@@ -1382,25 +1382,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N14" t="n">
-        <v>6.554271697998047</v>
+        <v>8.026138305664062</v>
       </c>
       <c r="O14" t="n">
-        <v>58.1</v>
+        <v>48.7</v>
       </c>
       <c r="P14" t="n">
         <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -1409,32 +1409,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12:08:19</t>
+          <t>12:21:14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4976.625</v>
+        <v>5092.3125</v>
       </c>
       <c r="C15" t="n">
-        <v>77683.53125</v>
+        <v>83637.78125</v>
       </c>
       <c r="D15" t="n">
-        <v>136.6875</v>
+        <v>143.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="n">
-        <v>68983436</v>
+        <v>73774637</v>
       </c>
       <c r="G15" t="n">
-        <v>44335756</v>
+        <v>47207278</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>316625712</v>
+        <v>335330084</v>
       </c>
       <c r="J15" t="n">
         <v>2496</v>
@@ -1449,25 +1449,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N15" t="n">
-        <v>6.556537628173828</v>
+        <v>8.02880859375</v>
       </c>
       <c r="O15" t="n">
-        <v>58.1</v>
+        <v>48.7</v>
       </c>
       <c r="P15" t="n">
         <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T15" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
@@ -1476,35 +1476,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12:08:20</t>
+          <t>12:21:15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4976.828125</v>
+        <v>5092.640625</v>
       </c>
       <c r="C16" t="n">
-        <v>77691.421875</v>
+        <v>83645.34375</v>
       </c>
       <c r="D16" t="n">
-        <v>136.6875</v>
+        <v>143.515625</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="n">
-        <v>68992032</v>
+        <v>73790300</v>
       </c>
       <c r="G16" t="n">
-        <v>44340588</v>
+        <v>47215740</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>316653612</v>
+        <v>335467353</v>
       </c>
       <c r="J16" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1516,25 +1516,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5462646484375</v>
+        <v>7.977184295654297</v>
       </c>
       <c r="O16" t="n">
-        <v>58.2</v>
+        <v>49</v>
       </c>
       <c r="P16" t="n">
         <v>7.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T16" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -1543,35 +1543,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12:08:21</t>
+          <t>12:21:16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4977.109375</v>
+        <v>5097.625</v>
       </c>
       <c r="C17" t="n">
-        <v>77699.0625</v>
+        <v>83647.96875</v>
       </c>
       <c r="D17" t="n">
-        <v>136.6875</v>
+        <v>143.515625</v>
       </c>
       <c r="E17" t="n">
-        <v>6.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>69008585</v>
+        <v>73808574</v>
       </c>
       <c r="G17" t="n">
-        <v>44350681</v>
+        <v>47237696</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>316792373</v>
+        <v>335551048</v>
       </c>
       <c r="J17" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1583,25 +1583,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N17" t="n">
-        <v>6.519325256347656</v>
+        <v>7.917156219482422</v>
       </c>
       <c r="O17" t="n">
-        <v>58.3</v>
+        <v>49.4</v>
       </c>
       <c r="P17" t="n">
         <v>7.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -1610,32 +1610,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12:08:22</t>
+          <t>12:21:17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4977.21875</v>
+        <v>5104.1875</v>
       </c>
       <c r="C18" t="n">
-        <v>77707</v>
+        <v>83649.296875</v>
       </c>
       <c r="D18" t="n">
-        <v>136.6875</v>
+        <v>143.5625</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>83.8</v>
       </c>
       <c r="F18" t="n">
-        <v>69013042</v>
+        <v>73821047</v>
       </c>
       <c r="G18" t="n">
-        <v>44353305</v>
+        <v>47247794</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>316816303</v>
+        <v>335593045</v>
       </c>
       <c r="J18" t="n">
         <v>2496</v>
@@ -1650,25 +1650,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N18" t="n">
-        <v>6.518100738525391</v>
+        <v>7.925323486328125</v>
       </c>
       <c r="O18" t="n">
-        <v>58.4</v>
+        <v>49.4</v>
       </c>
       <c r="P18" t="n">
         <v>7.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
@@ -1677,32 +1677,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12:08:23</t>
+          <t>12:21:18</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4977.34375</v>
+        <v>5111.109375</v>
       </c>
       <c r="C19" t="n">
-        <v>77714.8125</v>
+        <v>83649.90625</v>
       </c>
       <c r="D19" t="n">
-        <v>136.6875</v>
+        <v>143.5625</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>92.5</v>
       </c>
       <c r="F19" t="n">
-        <v>69022282</v>
+        <v>73828323</v>
       </c>
       <c r="G19" t="n">
-        <v>44358788</v>
+        <v>47254030</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>316877817</v>
+        <v>335653843</v>
       </c>
       <c r="J19" t="n">
         <v>2496</v>
@@ -1717,25 +1717,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N19" t="n">
-        <v>6.519477844238281</v>
+        <v>7.918041229248047</v>
       </c>
       <c r="O19" t="n">
-        <v>58.3</v>
+        <v>49.4</v>
       </c>
       <c r="P19" t="n">
         <v>7.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T19" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
@@ -1744,32 +1744,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12:08:24</t>
+          <t>12:21:19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4977.40625</v>
+        <v>5117.578125</v>
       </c>
       <c r="C20" t="n">
-        <v>77722.75</v>
+        <v>83651.375</v>
       </c>
       <c r="D20" t="n">
-        <v>136.6875</v>
+        <v>143.5625</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>69026366</v>
+        <v>73833773</v>
       </c>
       <c r="G20" t="n">
-        <v>44361135</v>
+        <v>47259175</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>316893337</v>
+        <v>335671345</v>
       </c>
       <c r="J20" t="n">
         <v>2496</v>
@@ -1784,25 +1784,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N20" t="n">
-        <v>6.529220581054688</v>
+        <v>7.932468414306641</v>
       </c>
       <c r="O20" t="n">
-        <v>58.3</v>
+        <v>49.3</v>
       </c>
       <c r="P20" t="n">
         <v>7.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T20" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
@@ -1811,32 +1811,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12:08:25</t>
+          <t>12:21:20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4977.515625</v>
+        <v>5123.875</v>
       </c>
       <c r="C21" t="n">
-        <v>77730.765625</v>
+        <v>83652.8125</v>
       </c>
       <c r="D21" t="n">
-        <v>136.6875</v>
+        <v>143.625</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>82.5</v>
       </c>
       <c r="F21" t="n">
-        <v>69035730</v>
+        <v>73843179</v>
       </c>
       <c r="G21" t="n">
-        <v>44366683</v>
+        <v>47266478</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>316916728</v>
+        <v>335697575</v>
       </c>
       <c r="J21" t="n">
         <v>2496</v>
@@ -1851,25 +1851,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N21" t="n">
-        <v>6.529335021972656</v>
+        <v>7.931388854980469</v>
       </c>
       <c r="O21" t="n">
-        <v>58.3</v>
+        <v>49.3</v>
       </c>
       <c r="P21" t="n">
         <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T21" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U21" t="b">
         <v>0</v>
@@ -1878,32 +1878,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12:08:26</t>
+          <t>12:21:21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4977.828125</v>
+        <v>5130.453125</v>
       </c>
       <c r="C22" t="n">
-        <v>77738.328125</v>
+        <v>83654.203125</v>
       </c>
       <c r="D22" t="n">
-        <v>136.703125</v>
+        <v>143.625</v>
       </c>
       <c r="E22" t="n">
-        <v>6.2</v>
+        <v>82.8</v>
       </c>
       <c r="F22" t="n">
-        <v>69046971</v>
+        <v>73851178</v>
       </c>
       <c r="G22" t="n">
-        <v>44373580</v>
+        <v>47270879</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>316947651</v>
+        <v>335725200</v>
       </c>
       <c r="J22" t="n">
         <v>2496</v>
@@ -1918,25 +1918,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N22" t="n">
-        <v>6.530876159667969</v>
+        <v>7.934719085693359</v>
       </c>
       <c r="O22" t="n">
-        <v>58.3</v>
+        <v>49.3</v>
       </c>
       <c r="P22" t="n">
         <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T22" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
@@ -1945,32 +1945,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12:08:27</t>
+          <t>12:21:22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4977.90625</v>
+        <v>5136.875</v>
       </c>
       <c r="C23" t="n">
-        <v>77746.40625</v>
+        <v>83655.609375</v>
       </c>
       <c r="D23" t="n">
-        <v>136.71875</v>
+        <v>143.640625</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1</v>
+        <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>69051931</v>
+        <v>73858346</v>
       </c>
       <c r="G23" t="n">
-        <v>44376632</v>
+        <v>47275372</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>316965846</v>
+        <v>335754896</v>
       </c>
       <c r="J23" t="n">
         <v>2496</v>
@@ -1985,25 +1985,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N23" t="n">
-        <v>6.532306671142578</v>
+        <v>7.936454772949219</v>
       </c>
       <c r="O23" t="n">
-        <v>58.3</v>
+        <v>49.3</v>
       </c>
       <c r="P23" t="n">
         <v>7.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T23" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U23" t="b">
         <v>0</v>
@@ -2012,32 +2012,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>12:08:28</t>
+          <t>12:21:23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4978.03125</v>
+        <v>5143.46875</v>
       </c>
       <c r="C24" t="n">
-        <v>77754.171875</v>
+        <v>83656.671875</v>
       </c>
       <c r="D24" t="n">
-        <v>136.71875</v>
+        <v>143.671875</v>
       </c>
       <c r="E24" t="n">
-        <v>6.4</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
-        <v>69062653</v>
+        <v>73862991</v>
       </c>
       <c r="G24" t="n">
-        <v>44382269</v>
+        <v>47279606</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>317034015</v>
+        <v>335791995</v>
       </c>
       <c r="J24" t="n">
         <v>2496</v>
@@ -2052,25 +2052,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N24" t="n">
-        <v>6.540813446044922</v>
+        <v>7.930397033691406</v>
       </c>
       <c r="O24" t="n">
-        <v>58.2</v>
+        <v>49.3</v>
       </c>
       <c r="P24" t="n">
         <v>7.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T24" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U24" t="b">
         <v>0</v>
@@ -2079,35 +2079,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12:08:29</t>
+          <t>12:21:24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4978.125</v>
+        <v>5150.1875</v>
       </c>
       <c r="C25" t="n">
-        <v>77762.125</v>
+        <v>83657.640625</v>
       </c>
       <c r="D25" t="n">
-        <v>136.71875</v>
+        <v>143.6875</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1</v>
+        <v>88.2</v>
       </c>
       <c r="F25" t="n">
-        <v>69066759</v>
+        <v>73870643</v>
       </c>
       <c r="G25" t="n">
-        <v>44384702</v>
+        <v>47285160</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>317046674</v>
+        <v>335834598</v>
       </c>
       <c r="J25" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2119,25 +2119,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N25" t="n">
-        <v>6.54339599609375</v>
+        <v>7.936359405517578</v>
       </c>
       <c r="O25" t="n">
-        <v>58.2</v>
+        <v>49.3</v>
       </c>
       <c r="P25" t="n">
         <v>7.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T25" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -2146,32 +2146,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12:08:30</t>
+          <t>12:21:25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4978.40625</v>
+        <v>5156.6875</v>
       </c>
       <c r="C26" t="n">
-        <v>77769.875</v>
+        <v>83659.109375</v>
       </c>
       <c r="D26" t="n">
-        <v>136.71875</v>
+        <v>143.6875</v>
       </c>
       <c r="E26" t="n">
-        <v>5.3</v>
+        <v>82</v>
       </c>
       <c r="F26" t="n">
-        <v>69072540</v>
+        <v>73876546</v>
       </c>
       <c r="G26" t="n">
-        <v>44388187</v>
+        <v>47288923</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>317065998</v>
+        <v>335886583</v>
       </c>
       <c r="J26" t="n">
         <v>2496</v>
@@ -2186,25 +2186,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N26" t="n">
-        <v>6.548435211181641</v>
+        <v>7.93695068359375</v>
       </c>
       <c r="O26" t="n">
-        <v>58.2</v>
+        <v>49.3</v>
       </c>
       <c r="P26" t="n">
         <v>7.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T26" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U26" t="b">
         <v>0</v>
@@ -2213,32 +2213,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12:08:31</t>
+          <t>12:21:26</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4978.46875</v>
+        <v>5163.359375</v>
       </c>
       <c r="C27" t="n">
-        <v>77777.890625</v>
+        <v>83660.28125</v>
       </c>
       <c r="D27" t="n">
-        <v>136.71875</v>
+        <v>143.6875</v>
       </c>
       <c r="E27" t="n">
-        <v>3.4</v>
+        <v>85.5</v>
       </c>
       <c r="F27" t="n">
-        <v>69076257</v>
+        <v>73884259</v>
       </c>
       <c r="G27" t="n">
-        <v>44390431</v>
+        <v>47293415</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>317079993</v>
+        <v>335913115</v>
       </c>
       <c r="J27" t="n">
         <v>2496</v>
@@ -2253,25 +2253,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N27" t="n">
-        <v>6.548500061035156</v>
+        <v>7.938621520996094</v>
       </c>
       <c r="O27" t="n">
-        <v>58.2</v>
+        <v>49.3</v>
       </c>
       <c r="P27" t="n">
         <v>7.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S27" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T27" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
@@ -2280,32 +2280,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12:08:33</t>
+          <t>12:21:27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4978.53125</v>
+        <v>5169.9375</v>
       </c>
       <c r="C28" t="n">
-        <v>77785.703125</v>
+        <v>83661.84375</v>
       </c>
       <c r="D28" t="n">
-        <v>136.71875</v>
+        <v>143.6875</v>
       </c>
       <c r="E28" t="n">
-        <v>2.9</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>69080127</v>
+        <v>73890486</v>
       </c>
       <c r="G28" t="n">
-        <v>44392709</v>
+        <v>47297152</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>317097320</v>
+        <v>335933378</v>
       </c>
       <c r="J28" t="n">
         <v>2496</v>
@@ -2320,25 +2320,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N28" t="n">
-        <v>6.545921325683594</v>
+        <v>7.938064575195312</v>
       </c>
       <c r="O28" t="n">
-        <v>58.2</v>
+        <v>49.3</v>
       </c>
       <c r="P28" t="n">
         <v>7.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T28" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U28" t="b">
         <v>0</v>
@@ -2347,35 +2347,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12:08:34</t>
+          <t>12:21:28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4978.703125</v>
+        <v>5176.59375</v>
       </c>
       <c r="C29" t="n">
-        <v>77793.578125</v>
+        <v>83663.09375</v>
       </c>
       <c r="D29" t="n">
-        <v>136.71875</v>
+        <v>143.734375</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>84.8</v>
       </c>
       <c r="F29" t="n">
-        <v>69089276</v>
+        <v>73896067</v>
       </c>
       <c r="G29" t="n">
-        <v>44398057</v>
+        <v>47301218</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>317159458</v>
+        <v>335955902</v>
       </c>
       <c r="J29" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2387,25 +2387,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N29" t="n">
-        <v>6.537578582763672</v>
+        <v>7.938930511474609</v>
       </c>
       <c r="O29" t="n">
-        <v>58.2</v>
+        <v>49.3</v>
       </c>
       <c r="P29" t="n">
         <v>7.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T29" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U29" t="b">
         <v>0</v>
@@ -2414,32 +2414,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12:08:35</t>
+          <t>12:21:29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4978.828125</v>
+        <v>5183.53125</v>
       </c>
       <c r="C30" t="n">
-        <v>77801.484375</v>
+        <v>83663.859375</v>
       </c>
       <c r="D30" t="n">
-        <v>136.71875</v>
+        <v>143.734375</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>69093564</v>
+        <v>73903216</v>
       </c>
       <c r="G30" t="n">
-        <v>44400594</v>
+        <v>47307069</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>317175025</v>
+        <v>336014058</v>
       </c>
       <c r="J30" t="n">
         <v>2496</v>
@@ -2454,25 +2454,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N30" t="n">
-        <v>6.550872802734375</v>
+        <v>7.932723999023437</v>
       </c>
       <c r="O30" t="n">
-        <v>58.1</v>
+        <v>49.3</v>
       </c>
       <c r="P30" t="n">
         <v>7.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S30" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T30" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U30" t="b">
         <v>0</v>
@@ -2481,32 +2481,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12:08:36</t>
+          <t>12:21:30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4978.875</v>
+        <v>5188.203125</v>
       </c>
       <c r="C31" t="n">
-        <v>77809.453125</v>
+        <v>83667.09375</v>
       </c>
       <c r="D31" t="n">
-        <v>136.734375</v>
+        <v>143.734375</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3</v>
+        <v>59.8</v>
       </c>
       <c r="F31" t="n">
-        <v>69098125</v>
+        <v>73908202</v>
       </c>
       <c r="G31" t="n">
-        <v>44403312</v>
+        <v>47311293</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>317190814</v>
+        <v>336033937</v>
       </c>
       <c r="J31" t="n">
         <v>2496</v>
@@ -2521,25 +2521,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N31" t="n">
-        <v>6.5517578125</v>
+        <v>7.990909576416016</v>
       </c>
       <c r="O31" t="n">
-        <v>58.1</v>
+        <v>48.9</v>
       </c>
       <c r="P31" t="n">
         <v>7.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S31" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T31" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U31" t="b">
         <v>0</v>
@@ -2548,32 +2548,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12:08:37</t>
+          <t>12:21:31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4979.03125</v>
+        <v>5188.28125</v>
       </c>
       <c r="C32" t="n">
-        <v>77817.265625</v>
+        <v>83674.96875</v>
       </c>
       <c r="D32" t="n">
-        <v>136.75</v>
+        <v>143.734375</v>
       </c>
       <c r="E32" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>69103657</v>
+        <v>73914949</v>
       </c>
       <c r="G32" t="n">
-        <v>44406342</v>
+        <v>47315373</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>317213429</v>
+        <v>336055266</v>
       </c>
       <c r="J32" t="n">
         <v>2496</v>
@@ -2588,25 +2588,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N32" t="n">
-        <v>6.552387237548828</v>
+        <v>7.989891052246094</v>
       </c>
       <c r="O32" t="n">
-        <v>58.1</v>
+        <v>49</v>
       </c>
       <c r="P32" t="n">
         <v>7.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S32" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T32" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U32" t="b">
         <v>0</v>
@@ -2615,35 +2615,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12:08:38</t>
+          <t>12:21:32</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4979.125</v>
+        <v>5188.640625</v>
       </c>
       <c r="C33" t="n">
-        <v>77825.234375</v>
+        <v>83682.703125</v>
       </c>
       <c r="D33" t="n">
-        <v>136.75</v>
+        <v>143.734375</v>
       </c>
       <c r="E33" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="F33" t="n">
-        <v>69111462</v>
+        <v>73924550</v>
       </c>
       <c r="G33" t="n">
-        <v>44411005</v>
+        <v>47321092</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>317236593</v>
+        <v>336081034</v>
       </c>
       <c r="J33" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2655,25 +2655,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N33" t="n">
-        <v>6.543037414550781</v>
+        <v>7.993598937988281</v>
       </c>
       <c r="O33" t="n">
-        <v>58.2</v>
+        <v>48.9</v>
       </c>
       <c r="P33" t="n">
         <v>7.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S33" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T33" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U33" t="b">
         <v>0</v>
@@ -2682,35 +2682,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12:08:39</t>
+          <t>12:21:33</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4979.40625</v>
+        <v>5189.5</v>
       </c>
       <c r="C34" t="n">
-        <v>77832.84375</v>
+        <v>83689.59375</v>
       </c>
       <c r="D34" t="n">
-        <v>136.78125</v>
+        <v>143.734375</v>
       </c>
       <c r="E34" t="n">
-        <v>8.1</v>
+        <v>15.5</v>
       </c>
       <c r="F34" t="n">
-        <v>69125699</v>
+        <v>73938437</v>
       </c>
       <c r="G34" t="n">
-        <v>44419268</v>
+        <v>47328987</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>317311863</v>
+        <v>336144948</v>
       </c>
       <c r="J34" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2722,25 +2722,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N34" t="n">
-        <v>6.539463043212891</v>
+        <v>7.969490051269531</v>
       </c>
       <c r="O34" t="n">
-        <v>58.2</v>
+        <v>49.1</v>
       </c>
       <c r="P34" t="n">
         <v>7.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S34" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T34" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U34" t="b">
         <v>0</v>
@@ -2749,32 +2749,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12:08:40</t>
+          <t>12:21:34</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4979.5</v>
+        <v>5189.625</v>
       </c>
       <c r="C35" t="n">
-        <v>77840.6875</v>
+        <v>83697.265625</v>
       </c>
       <c r="D35" t="n">
-        <v>136.796875</v>
+        <v>143.765625</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5</v>
+        <v>6.7</v>
       </c>
       <c r="F35" t="n">
-        <v>69133986</v>
+        <v>73956402</v>
       </c>
       <c r="G35" t="n">
-        <v>44424125</v>
+        <v>47339379</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>317333319</v>
+        <v>336229080</v>
       </c>
       <c r="J35" t="n">
         <v>2496</v>
@@ -2789,25 +2789,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N35" t="n">
-        <v>6.538005828857422</v>
+        <v>7.971523284912109</v>
       </c>
       <c r="O35" t="n">
-        <v>58.2</v>
+        <v>49.1</v>
       </c>
       <c r="P35" t="n">
         <v>7.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S35" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T35" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U35" t="b">
         <v>0</v>
@@ -2816,32 +2816,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12:08:41</t>
+          <t>12:21:35</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4979.609375</v>
+        <v>5189.765625</v>
       </c>
       <c r="C36" t="n">
-        <v>77848.734375</v>
+        <v>83705.109375</v>
       </c>
       <c r="D36" t="n">
-        <v>136.796875</v>
+        <v>143.765625</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="F36" t="n">
-        <v>69144192</v>
+        <v>73964402</v>
       </c>
       <c r="G36" t="n">
-        <v>44430673</v>
+        <v>47344185</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>317357609</v>
+        <v>336268164</v>
       </c>
       <c r="J36" t="n">
         <v>2496</v>
@@ -2856,25 +2856,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N36" t="n">
-        <v>6.537513732910156</v>
+        <v>7.970767974853516</v>
       </c>
       <c r="O36" t="n">
-        <v>58.2</v>
+        <v>49.1</v>
       </c>
       <c r="P36" t="n">
         <v>7.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S36" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T36" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U36" t="b">
         <v>0</v>
@@ -2883,32 +2883,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12:08:42</t>
+          <t>12:21:36</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4979.734375</v>
+        <v>5189.875</v>
       </c>
       <c r="C37" t="n">
-        <v>77856.59375</v>
+        <v>83712.859375</v>
       </c>
       <c r="D37" t="n">
-        <v>136.796875</v>
+        <v>143.765625</v>
       </c>
       <c r="E37" t="n">
         <v>3.5</v>
       </c>
       <c r="F37" t="n">
-        <v>69149132</v>
+        <v>73971767</v>
       </c>
       <c r="G37" t="n">
-        <v>44433560</v>
+        <v>47348468</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>317382571</v>
+        <v>336293918</v>
       </c>
       <c r="J37" t="n">
         <v>2496</v>
@@ -2923,25 +2923,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N37" t="n">
-        <v>6.537467956542969</v>
+        <v>7.971000671386719</v>
       </c>
       <c r="O37" t="n">
-        <v>58.2</v>
+        <v>49.1</v>
       </c>
       <c r="P37" t="n">
         <v>7.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.407970428466797</v>
+        <v>7.413806915283203</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0920295715332031</v>
+        <v>0.08619308471679681</v>
       </c>
       <c r="S37" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T37" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U37" t="b">
         <v>0</v>
@@ -2950,67 +2950,201 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12:08:43</t>
+          <t>12:21:37</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4979.78125</v>
+        <v>5189.875</v>
       </c>
       <c r="C38" t="n">
-        <v>77864.625</v>
+        <v>83720.96875</v>
       </c>
       <c r="D38" t="n">
-        <v>136.796875</v>
+        <v>143.78125</v>
       </c>
       <c r="E38" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="F38" t="n">
-        <v>69152418</v>
+        <v>73974796</v>
       </c>
       <c r="G38" t="n">
-        <v>44435514</v>
+        <v>47350204</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>317394379</v>
+        <v>336303614</v>
       </c>
       <c r="J38" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M38" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7.971813201904297</v>
+      </c>
+      <c r="O38" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>7.413806915283203</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.08619308471679681</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>73</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12:21:38</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5190</v>
+      </c>
+      <c r="C39" t="n">
+        <v>83728.765625</v>
+      </c>
+      <c r="D39" t="n">
+        <v>143.796875</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>73978192</v>
+      </c>
+      <c r="G39" t="n">
+        <v>47352252</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>336315186</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M39" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7.971118927001953</v>
+      </c>
+      <c r="O39" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7.413806915283203</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.08619308471679681</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>73</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12:21:39</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5190.1875</v>
+      </c>
+      <c r="C40" t="n">
+        <v>83736.59375</v>
+      </c>
+      <c r="D40" t="n">
+        <v>143.8125</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>73987420</v>
+      </c>
+      <c r="G40" t="n">
+        <v>47357450</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>336378555</v>
+      </c>
+      <c r="J40" t="n">
         <v>998</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2496</v>
-      </c>
-      <c r="M38" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="N38" t="n">
-        <v>6.538341522216797</v>
-      </c>
-      <c r="O38" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="P38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>7.407970428466797</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.0920295715332031</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>77</v>
-      </c>
-      <c r="U38" t="b">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M40" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7.982856750488281</v>
+      </c>
+      <c r="O40" t="n">
+        <v>49</v>
+      </c>
+      <c r="P40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7.413806915283203</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.08619308471679681</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>73</v>
+      </c>
+      <c r="U40" t="b">
         <v>0</v>
       </c>
     </row>

--- a/labelled_dataset.xlsx
+++ b/labelled_dataset.xlsx
@@ -538,35 +538,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12:19:44</t>
+          <t>17:34:03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8375.21875</v>
+        <v>9541.359375</v>
       </c>
       <c r="C2" t="n">
-        <v>252747.375</v>
+        <v>334280.84375</v>
       </c>
       <c r="D2" t="n">
-        <v>234.09375</v>
+        <v>293.65625</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>171995729</v>
+        <v>220544322</v>
       </c>
       <c r="G2" t="n">
-        <v>114335329</v>
+        <v>143207512</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>778084794</v>
+        <v>948720123</v>
       </c>
       <c r="J2" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -578,25 +578,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N2" t="n">
-        <v>6.262592315673828</v>
+        <v>6.299945831298828</v>
       </c>
       <c r="O2" t="n">
-        <v>60</v>
+        <v>59.7</v>
       </c>
       <c r="P2" t="n">
         <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R2" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S2" t="n">
         <v>1.1</v>
       </c>
       <c r="T2" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -605,32 +605,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12:19:45</t>
+          <t>17:34:05</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8375.421875</v>
+        <v>9541.46875</v>
       </c>
       <c r="C3" t="n">
-        <v>252757.828125</v>
+        <v>334291.265625</v>
       </c>
       <c r="D3" t="n">
-        <v>234.125</v>
+        <v>293.671875</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>172005087</v>
+        <v>220560551</v>
       </c>
       <c r="G3" t="n">
-        <v>114340675</v>
+        <v>143216903</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>778166267</v>
+        <v>948816389</v>
       </c>
       <c r="J3" t="n">
         <v>2496</v>
@@ -645,25 +645,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N3" t="n">
-        <v>6.270183563232422</v>
+        <v>6.295131683349609</v>
       </c>
       <c r="O3" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="P3" t="n">
         <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S3" t="n">
         <v>1.1</v>
       </c>
       <c r="T3" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -672,32 +672,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12:19:46</t>
+          <t>17:34:06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8375.671875</v>
+        <v>9541.8125</v>
       </c>
       <c r="C4" t="n">
-        <v>252765.46875</v>
+        <v>334298.890625</v>
       </c>
       <c r="D4" t="n">
-        <v>234.140625</v>
+        <v>293.671875</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F4" t="n">
-        <v>172022217</v>
+        <v>220579623</v>
       </c>
       <c r="G4" t="n">
-        <v>114350528</v>
+        <v>143227381</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>778237452</v>
+        <v>948884735</v>
       </c>
       <c r="J4" t="n">
         <v>2496</v>
@@ -712,25 +712,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N4" t="n">
-        <v>6.267425537109375</v>
+        <v>6.282386779785156</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="P4" t="n">
         <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S4" t="n">
         <v>1.1</v>
       </c>
       <c r="T4" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -739,32 +739,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:19:47</t>
+          <t>17:34:07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8376.234375</v>
+        <v>9542.046875</v>
       </c>
       <c r="C5" t="n">
-        <v>252772.796875</v>
+        <v>334306.484375</v>
       </c>
       <c r="D5" t="n">
-        <v>234.15625</v>
+        <v>293.6875</v>
       </c>
       <c r="E5" t="n">
-        <v>11.3</v>
+        <v>8.6</v>
       </c>
       <c r="F5" t="n">
-        <v>172039000</v>
+        <v>220599573</v>
       </c>
       <c r="G5" t="n">
-        <v>114360056</v>
+        <v>143238628</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>778294489</v>
+        <v>948964912</v>
       </c>
       <c r="J5" t="n">
         <v>2496</v>
@@ -779,25 +779,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N5" t="n">
-        <v>6.256732940673828</v>
+        <v>6.284557342529297</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="P5" t="n">
         <v>7.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S5" t="n">
         <v>1.1</v>
       </c>
       <c r="T5" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -806,32 +806,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:19:48</t>
+          <t>17:34:08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8376.40625</v>
+        <v>9542.59375</v>
       </c>
       <c r="C6" t="n">
-        <v>252780.578125</v>
+        <v>334313.875</v>
       </c>
       <c r="D6" t="n">
-        <v>234.171875</v>
+        <v>293.703125</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3</v>
+        <v>9.9</v>
       </c>
       <c r="F6" t="n">
-        <v>172056345</v>
+        <v>220614540</v>
       </c>
       <c r="G6" t="n">
-        <v>114370098</v>
+        <v>143247137</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>778332928</v>
+        <v>949096501</v>
       </c>
       <c r="J6" t="n">
         <v>2496</v>
@@ -846,25 +846,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N6" t="n">
-        <v>6.257526397705078</v>
+        <v>6.251483917236328</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="P6" t="n">
         <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S6" t="n">
         <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -873,35 +873,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12:19:49</t>
+          <t>17:34:09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8376.671875</v>
+        <v>9542.8125</v>
       </c>
       <c r="C7" t="n">
-        <v>252788.171875</v>
+        <v>334321.546875</v>
       </c>
       <c r="D7" t="n">
-        <v>234.171875</v>
+        <v>293.75</v>
       </c>
       <c r="E7" t="n">
         <v>5.8</v>
       </c>
       <c r="F7" t="n">
-        <v>172072999</v>
+        <v>220635998</v>
       </c>
       <c r="G7" t="n">
-        <v>114380428</v>
+        <v>143260941</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>778407915</v>
+        <v>949190927</v>
       </c>
       <c r="J7" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N7" t="n">
-        <v>6.210247039794922</v>
+        <v>6.20965576171875</v>
       </c>
       <c r="O7" t="n">
         <v>60.3</v>
@@ -922,16 +922,16 @@
         <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S7" t="n">
         <v>1.1</v>
       </c>
       <c r="T7" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -940,32 +940,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12:19:50</t>
+          <t>17:34:10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8377.046875</v>
+        <v>9543.203125</v>
       </c>
       <c r="C8" t="n">
-        <v>252795.8125</v>
+        <v>334329.125</v>
       </c>
       <c r="D8" t="n">
-        <v>234.171875</v>
+        <v>293.75</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="F8" t="n">
-        <v>172083445</v>
+        <v>220653837</v>
       </c>
       <c r="G8" t="n">
-        <v>114387816</v>
+        <v>143272114</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>778460557</v>
+        <v>949263569</v>
       </c>
       <c r="J8" t="n">
         <v>2496</v>
@@ -980,25 +980,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N8" t="n">
-        <v>6.179035186767578</v>
+        <v>6.144363403320312</v>
       </c>
       <c r="O8" t="n">
-        <v>60.5</v>
+        <v>60.7</v>
       </c>
       <c r="P8" t="n">
         <v>7.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S8" t="n">
         <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1007,32 +1007,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12:19:51</t>
+          <t>17:34:11</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8377.296875</v>
+        <v>9543.25</v>
       </c>
       <c r="C9" t="n">
-        <v>252803.453125</v>
+        <v>334336.921875</v>
       </c>
       <c r="D9" t="n">
-        <v>234.171875</v>
+        <v>293.75</v>
       </c>
       <c r="E9" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>172099423</v>
+        <v>220663207</v>
       </c>
       <c r="G9" t="n">
-        <v>114397492</v>
+        <v>143277690</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>778549508</v>
+        <v>949294361</v>
       </c>
       <c r="J9" t="n">
         <v>2496</v>
@@ -1047,25 +1047,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N9" t="n">
-        <v>6.160366058349609</v>
+        <v>6.143035888671875</v>
       </c>
       <c r="O9" t="n">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
       <c r="P9" t="n">
         <v>7.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S9" t="n">
         <v>1.1</v>
       </c>
       <c r="T9" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1074,35 +1074,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12:19:52</t>
+          <t>17:34:12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8377.359375</v>
+        <v>9543.515625</v>
       </c>
       <c r="C10" t="n">
-        <v>252811.390625</v>
+        <v>334344.65625</v>
       </c>
       <c r="D10" t="n">
-        <v>234.171875</v>
+        <v>293.765625</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>172106557</v>
+        <v>220672869</v>
       </c>
       <c r="G10" t="n">
-        <v>114401747</v>
+        <v>143283255</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>778572403</v>
+        <v>949357705</v>
       </c>
       <c r="J10" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1114,25 +1114,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N10" t="n">
-        <v>6.160987854003906</v>
+        <v>6.142707824707031</v>
       </c>
       <c r="O10" t="n">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
       <c r="P10" t="n">
         <v>7.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R10" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S10" t="n">
         <v>1.1</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1141,32 +1141,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12:19:53</t>
+          <t>17:34:13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8377.65625</v>
+        <v>9543.890625</v>
       </c>
       <c r="C11" t="n">
-        <v>252819.328125</v>
+        <v>334352.3125</v>
       </c>
       <c r="D11" t="n">
-        <v>234.1875</v>
+        <v>293.78125</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="F11" t="n">
-        <v>172121969</v>
+        <v>220682941</v>
       </c>
       <c r="G11" t="n">
-        <v>114410749</v>
+        <v>143288732</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>778613221</v>
+        <v>949396604</v>
       </c>
       <c r="J11" t="n">
         <v>2496</v>
@@ -1181,25 +1181,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N11" t="n">
-        <v>6.256343841552734</v>
+        <v>6.130481719970703</v>
       </c>
       <c r="O11" t="n">
-        <v>60</v>
+        <v>60.8</v>
       </c>
       <c r="P11" t="n">
         <v>7.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R11" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S11" t="n">
         <v>1.1</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -1208,32 +1208,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12:19:54</t>
+          <t>17:34:14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8378.296875</v>
+        <v>9544.140625</v>
       </c>
       <c r="C12" t="n">
-        <v>252826.5</v>
+        <v>334359.890625</v>
       </c>
       <c r="D12" t="n">
-        <v>234.1875</v>
+        <v>293.78125</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>6.7</v>
       </c>
       <c r="F12" t="n">
-        <v>172133988</v>
+        <v>220697027</v>
       </c>
       <c r="G12" t="n">
-        <v>114417739</v>
+        <v>143296996</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>778669452</v>
+        <v>949448423</v>
       </c>
       <c r="J12" t="n">
         <v>2496</v>
@@ -1248,25 +1248,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N12" t="n">
-        <v>6.250244140625</v>
+        <v>6.141311645507812</v>
       </c>
       <c r="O12" t="n">
-        <v>60.1</v>
+        <v>60.8</v>
       </c>
       <c r="P12" t="n">
         <v>7.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S12" t="n">
         <v>1.1</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1275,32 +1275,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12:19:55</t>
+          <t>17:34:15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8378.3125</v>
+        <v>9544.171875</v>
       </c>
       <c r="C13" t="n">
-        <v>252834.4375</v>
+        <v>334368.015625</v>
       </c>
       <c r="D13" t="n">
-        <v>234.1875</v>
+        <v>293.78125</v>
       </c>
       <c r="E13" t="n">
         <v>1.7</v>
       </c>
       <c r="F13" t="n">
-        <v>172139621</v>
+        <v>220708377</v>
       </c>
       <c r="G13" t="n">
-        <v>114420940</v>
+        <v>143303753</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>778685265</v>
+        <v>949471283</v>
       </c>
       <c r="J13" t="n">
         <v>2496</v>
@@ -1315,25 +1315,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N13" t="n">
-        <v>6.251129150390625</v>
+        <v>6.142440795898438</v>
       </c>
       <c r="O13" t="n">
-        <v>60.1</v>
+        <v>60.8</v>
       </c>
       <c r="P13" t="n">
         <v>7.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S13" t="n">
         <v>1.1</v>
       </c>
       <c r="T13" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -1342,32 +1342,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12:19:56</t>
+          <t>17:34:16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8378.765625</v>
+        <v>9544.28125</v>
       </c>
       <c r="C14" t="n">
-        <v>252841.875</v>
+        <v>334375.921875</v>
       </c>
       <c r="D14" t="n">
-        <v>234.203125</v>
+        <v>293.78125</v>
       </c>
       <c r="E14" t="n">
-        <v>10.2</v>
+        <v>2.7</v>
       </c>
       <c r="F14" t="n">
-        <v>172155086</v>
+        <v>220722010</v>
       </c>
       <c r="G14" t="n">
-        <v>114430235</v>
+        <v>143311640</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>778760146</v>
+        <v>949498100</v>
       </c>
       <c r="J14" t="n">
         <v>2496</v>
@@ -1382,25 +1382,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N14" t="n">
-        <v>6.253761291503906</v>
+        <v>6.141399383544922</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>60.8</v>
       </c>
       <c r="P14" t="n">
         <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R14" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S14" t="n">
         <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -1409,32 +1409,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12:19:57</t>
+          <t>17:34:17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8378.984375</v>
+        <v>9544.46875</v>
       </c>
       <c r="C15" t="n">
-        <v>252849.71875</v>
+        <v>334383.640625</v>
       </c>
       <c r="D15" t="n">
-        <v>234.203125</v>
+        <v>293.8125</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="F15" t="n">
-        <v>172162102</v>
+        <v>220736085</v>
       </c>
       <c r="G15" t="n">
-        <v>114434242</v>
+        <v>143319863</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>778781009</v>
+        <v>949567236</v>
       </c>
       <c r="J15" t="n">
         <v>2496</v>
@@ -1449,25 +1449,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N15" t="n">
-        <v>6.253456115722656</v>
+        <v>6.140613555908203</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>60.8</v>
       </c>
       <c r="P15" t="n">
         <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R15" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S15" t="n">
         <v>1.1</v>
       </c>
       <c r="T15" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
@@ -1476,32 +1476,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12:19:58</t>
+          <t>17:34:18</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8379.21875</v>
+        <v>9544.6875</v>
       </c>
       <c r="C16" t="n">
-        <v>252857.515625</v>
+        <v>334391.390625</v>
       </c>
       <c r="D16" t="n">
-        <v>234.203125</v>
+        <v>293.828125</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F16" t="n">
-        <v>172172317</v>
+        <v>220745926</v>
       </c>
       <c r="G16" t="n">
-        <v>114440568</v>
+        <v>143325544</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>778810396</v>
+        <v>949593839</v>
       </c>
       <c r="J16" t="n">
         <v>2496</v>
@@ -1516,25 +1516,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N16" t="n">
-        <v>6.256374359130859</v>
+        <v>6.139171600341797</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>60.8</v>
       </c>
       <c r="P16" t="n">
         <v>7.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.418903350830078</v>
+        <v>7.415760040283203</v>
       </c>
       <c r="R16" t="n">
-        <v>0.08109664916992181</v>
+        <v>0.08423995971679681</v>
       </c>
       <c r="S16" t="n">
         <v>1.1</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>

--- a/labelled_dataset.xlsx
+++ b/labelled_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,32 +538,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17:34:03</t>
+          <t>19:25:36</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9541.359375</v>
+        <v>10011</v>
       </c>
       <c r="C2" t="n">
-        <v>334280.84375</v>
+        <v>357463.6718749999</v>
       </c>
       <c r="D2" t="n">
-        <v>293.65625</v>
+        <v>317.140625</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="F2" t="n">
-        <v>220544322</v>
+        <v>239693173</v>
       </c>
       <c r="G2" t="n">
-        <v>143207512</v>
+        <v>154628979</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>948720123</v>
+        <v>1028228344</v>
       </c>
       <c r="J2" t="n">
         <v>998</v>
@@ -578,25 +578,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N2" t="n">
-        <v>6.299945831298828</v>
+        <v>6.384521484375</v>
       </c>
       <c r="O2" t="n">
-        <v>59.7</v>
+        <v>59.2</v>
       </c>
       <c r="P2" t="n">
         <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R2" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -605,32 +605,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17:34:05</t>
+          <t>19:25:37</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9541.46875</v>
+        <v>10011.15625</v>
       </c>
       <c r="C3" t="n">
-        <v>334291.265625</v>
+        <v>357474.0781249999</v>
       </c>
       <c r="D3" t="n">
-        <v>293.671875</v>
+        <v>317.140625</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="F3" t="n">
-        <v>220560551</v>
+        <v>239699747</v>
       </c>
       <c r="G3" t="n">
-        <v>143216903</v>
+        <v>154632709</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>948816389</v>
+        <v>1028310560</v>
       </c>
       <c r="J3" t="n">
         <v>2496</v>
@@ -645,25 +645,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N3" t="n">
-        <v>6.295131683349609</v>
+        <v>6.401626586914063</v>
       </c>
       <c r="O3" t="n">
-        <v>59.8</v>
+        <v>59.1</v>
       </c>
       <c r="P3" t="n">
         <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -672,32 +672,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17:34:06</t>
+          <t>19:25:38</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9541.8125</v>
+        <v>10011.703125</v>
       </c>
       <c r="C4" t="n">
-        <v>334298.890625</v>
+        <v>357481.5156249999</v>
       </c>
       <c r="D4" t="n">
-        <v>293.671875</v>
+        <v>317.15625</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5</v>
+        <v>11.8</v>
       </c>
       <c r="F4" t="n">
-        <v>220579623</v>
+        <v>239721915</v>
       </c>
       <c r="G4" t="n">
-        <v>143227381</v>
+        <v>154645021</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>948884735</v>
+        <v>1028425437</v>
       </c>
       <c r="J4" t="n">
         <v>2496</v>
@@ -712,25 +712,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N4" t="n">
-        <v>6.282386779785156</v>
+        <v>6.399555206298828</v>
       </c>
       <c r="O4" t="n">
-        <v>59.9</v>
+        <v>59.1</v>
       </c>
       <c r="P4" t="n">
         <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -739,32 +739,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17:34:07</t>
+          <t>19:25:39</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9542.046875</v>
+        <v>10011.84375</v>
       </c>
       <c r="C5" t="n">
-        <v>334306.484375</v>
+        <v>357489.2031249999</v>
       </c>
       <c r="D5" t="n">
-        <v>293.6875</v>
+        <v>317.171875</v>
       </c>
       <c r="E5" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="F5" t="n">
-        <v>220599573</v>
+        <v>239736687</v>
       </c>
       <c r="G5" t="n">
-        <v>143238628</v>
+        <v>154653828</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>948964912</v>
+        <v>1028455200</v>
       </c>
       <c r="J5" t="n">
         <v>2496</v>
@@ -779,25 +779,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N5" t="n">
-        <v>6.284557342529297</v>
+        <v>6.399738311767578</v>
       </c>
       <c r="O5" t="n">
-        <v>59.8</v>
+        <v>59.1</v>
       </c>
       <c r="P5" t="n">
         <v>7.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -806,32 +806,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:34:08</t>
+          <t>19:25:40</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9542.59375</v>
+        <v>10012.46875</v>
       </c>
       <c r="C6" t="n">
-        <v>334313.875</v>
+        <v>357496.4374999999</v>
       </c>
       <c r="D6" t="n">
-        <v>293.703125</v>
+        <v>317.171875</v>
       </c>
       <c r="E6" t="n">
-        <v>9.9</v>
+        <v>11.6</v>
       </c>
       <c r="F6" t="n">
-        <v>220614540</v>
+        <v>239751509</v>
       </c>
       <c r="G6" t="n">
-        <v>143247137</v>
+        <v>154662057</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>949096501</v>
+        <v>1028586960</v>
       </c>
       <c r="J6" t="n">
         <v>2496</v>
@@ -846,25 +846,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N6" t="n">
-        <v>6.251483917236328</v>
+        <v>6.37469482421875</v>
       </c>
       <c r="O6" t="n">
-        <v>60.1</v>
+        <v>59.3</v>
       </c>
       <c r="P6" t="n">
         <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T6" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -873,35 +873,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17:34:09</t>
+          <t>19:25:41</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9542.8125</v>
+        <v>10012.796875</v>
       </c>
       <c r="C7" t="n">
-        <v>334321.546875</v>
+        <v>357504.1718749999</v>
       </c>
       <c r="D7" t="n">
-        <v>293.75</v>
+        <v>317.171875</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="F7" t="n">
-        <v>220635998</v>
+        <v>239775390</v>
       </c>
       <c r="G7" t="n">
-        <v>143260941</v>
+        <v>154676865</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>949190927</v>
+        <v>1028688423</v>
       </c>
       <c r="J7" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -913,25 +913,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N7" t="n">
-        <v>6.20965576171875</v>
+        <v>6.339828491210938</v>
       </c>
       <c r="O7" t="n">
-        <v>60.3</v>
+        <v>59.5</v>
       </c>
       <c r="P7" t="n">
         <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T7" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -940,32 +940,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17:34:10</t>
+          <t>19:25:42</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9543.203125</v>
+        <v>10013.0625</v>
       </c>
       <c r="C8" t="n">
-        <v>334329.125</v>
+        <v>357511.7968749999</v>
       </c>
       <c r="D8" t="n">
-        <v>293.75</v>
+        <v>317.171875</v>
       </c>
       <c r="E8" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="F8" t="n">
-        <v>220653837</v>
+        <v>239792965</v>
       </c>
       <c r="G8" t="n">
-        <v>143272114</v>
+        <v>154688043</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>949263569</v>
+        <v>1028759257</v>
       </c>
       <c r="J8" t="n">
         <v>2496</v>
@@ -980,25 +980,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N8" t="n">
-        <v>6.144363403320312</v>
+        <v>6.301555633544922</v>
       </c>
       <c r="O8" t="n">
-        <v>60.7</v>
+        <v>59.7</v>
       </c>
       <c r="P8" t="n">
         <v>7.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1007,32 +1007,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17:34:11</t>
+          <t>19:25:43</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9543.25</v>
+        <v>10013.171875</v>
       </c>
       <c r="C9" t="n">
-        <v>334336.921875</v>
+        <v>357519.5312499999</v>
       </c>
       <c r="D9" t="n">
-        <v>293.75</v>
+        <v>317.1875</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="F9" t="n">
-        <v>220663207</v>
+        <v>239805054</v>
       </c>
       <c r="G9" t="n">
-        <v>143277690</v>
+        <v>154695559</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>949294361</v>
+        <v>1028841240</v>
       </c>
       <c r="J9" t="n">
         <v>2496</v>
@@ -1047,25 +1047,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N9" t="n">
-        <v>6.143035888671875</v>
+        <v>6.29351806640625</v>
       </c>
       <c r="O9" t="n">
-        <v>60.8</v>
+        <v>59.8</v>
       </c>
       <c r="P9" t="n">
         <v>7.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1074,32 +1074,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17:34:12</t>
+          <t>19:25:44</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9543.515625</v>
+        <v>10013.40625</v>
       </c>
       <c r="C10" t="n">
-        <v>334344.65625</v>
+        <v>357527.2031249999</v>
       </c>
       <c r="D10" t="n">
-        <v>293.765625</v>
+        <v>317.234375</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F10" t="n">
-        <v>220672869</v>
+        <v>239822564</v>
       </c>
       <c r="G10" t="n">
-        <v>143283255</v>
+        <v>154705375</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>949357705</v>
+        <v>1028908220</v>
       </c>
       <c r="J10" t="n">
         <v>2496</v>
@@ -1114,25 +1114,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N10" t="n">
-        <v>6.142707824707031</v>
+        <v>6.278858184814453</v>
       </c>
       <c r="O10" t="n">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="P10" t="n">
         <v>7.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R10" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1141,32 +1141,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17:34:13</t>
+          <t>19:25:45</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9543.890625</v>
+        <v>10013.984375</v>
       </c>
       <c r="C11" t="n">
-        <v>334352.3125</v>
+        <v>357534.6562499999</v>
       </c>
       <c r="D11" t="n">
-        <v>293.78125</v>
+        <v>317.25</v>
       </c>
       <c r="E11" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="F11" t="n">
-        <v>220682941</v>
+        <v>239833292</v>
       </c>
       <c r="G11" t="n">
-        <v>143288732</v>
+        <v>154712005</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>949396604</v>
+        <v>1028935737</v>
       </c>
       <c r="J11" t="n">
         <v>2496</v>
@@ -1181,25 +1181,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N11" t="n">
-        <v>6.130481719970703</v>
+        <v>6.281078338623047</v>
       </c>
       <c r="O11" t="n">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="P11" t="n">
         <v>7.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R11" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -1208,32 +1208,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17:34:14</t>
+          <t>19:25:46</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9544.140625</v>
+        <v>10014.078125</v>
       </c>
       <c r="C12" t="n">
-        <v>334359.890625</v>
+        <v>357542.5468749999</v>
       </c>
       <c r="D12" t="n">
-        <v>293.78125</v>
+        <v>317.25</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="F12" t="n">
-        <v>220697027</v>
+        <v>239843517</v>
       </c>
       <c r="G12" t="n">
-        <v>143296996</v>
+        <v>154718040</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>949448423</v>
+        <v>1028964745</v>
       </c>
       <c r="J12" t="n">
         <v>2496</v>
@@ -1248,25 +1248,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N12" t="n">
-        <v>6.141311645507812</v>
+        <v>6.284732818603516</v>
       </c>
       <c r="O12" t="n">
-        <v>60.8</v>
+        <v>59.8</v>
       </c>
       <c r="P12" t="n">
         <v>7.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1275,32 +1275,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17:34:15</t>
+          <t>19:25:47</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9544.171875</v>
+        <v>10014.234375</v>
       </c>
       <c r="C13" t="n">
-        <v>334368.015625</v>
+        <v>357550.2968749999</v>
       </c>
       <c r="D13" t="n">
-        <v>293.78125</v>
+        <v>317.296875</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="F13" t="n">
-        <v>220708377</v>
+        <v>239854323</v>
       </c>
       <c r="G13" t="n">
-        <v>143303753</v>
+        <v>154724800</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>949471283</v>
+        <v>1028988403</v>
       </c>
       <c r="J13" t="n">
         <v>2496</v>
@@ -1315,25 +1315,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N13" t="n">
-        <v>6.142440795898438</v>
+        <v>6.297016143798828</v>
       </c>
       <c r="O13" t="n">
-        <v>60.8</v>
+        <v>59.8</v>
       </c>
       <c r="P13" t="n">
         <v>7.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T13" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -1342,32 +1342,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17:34:16</t>
+          <t>19:25:48</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9544.28125</v>
+        <v>10014.546875</v>
       </c>
       <c r="C14" t="n">
-        <v>334375.921875</v>
+        <v>357557.9218749999</v>
       </c>
       <c r="D14" t="n">
-        <v>293.78125</v>
+        <v>317.296875</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>220722010</v>
+        <v>239868781</v>
       </c>
       <c r="G14" t="n">
-        <v>143311640</v>
+        <v>154733143</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>949498100</v>
+        <v>1029065257</v>
       </c>
       <c r="J14" t="n">
         <v>2496</v>
@@ -1382,161 +1382,27 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N14" t="n">
-        <v>6.141399383544922</v>
+        <v>6.282184600830078</v>
       </c>
       <c r="O14" t="n">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="P14" t="n">
         <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.415760040283203</v>
+        <v>7.409454345703125</v>
       </c>
       <c r="R14" t="n">
-        <v>0.08423995971679681</v>
+        <v>0.090545654296875</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>17:34:17</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9544.46875</v>
-      </c>
-      <c r="C15" t="n">
-        <v>334383.640625</v>
-      </c>
-      <c r="D15" t="n">
-        <v>293.8125</v>
-      </c>
-      <c r="E15" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>220736085</v>
-      </c>
-      <c r="G15" t="n">
-        <v>143319863</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>949567236</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2496</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2496</v>
-      </c>
-      <c r="M15" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="N15" t="n">
-        <v>6.140613555908203</v>
-      </c>
-      <c r="O15" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="P15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>7.415760040283203</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.08423995971679681</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>71</v>
-      </c>
-      <c r="U15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>17:34:18</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>9544.6875</v>
-      </c>
-      <c r="C16" t="n">
-        <v>334391.390625</v>
-      </c>
-      <c r="D16" t="n">
-        <v>293.828125</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>220745926</v>
-      </c>
-      <c r="G16" t="n">
-        <v>143325544</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>949593839</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2496</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2496</v>
-      </c>
-      <c r="M16" t="n">
-        <v>15.6518669128418</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6.139171600341797</v>
-      </c>
-      <c r="O16" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7.415760040283203</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.08423995971679681</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>71</v>
-      </c>
-      <c r="U16" t="b">
         <v>0</v>
       </c>
     </row>

--- a/labelled_dataset.xlsx
+++ b/labelled_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,35 +538,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19:25:36</t>
+          <t>11:14:21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10011</v>
+        <v>10655.296875</v>
       </c>
       <c r="C2" t="n">
-        <v>357463.6718749999</v>
+        <v>375387</v>
       </c>
       <c r="D2" t="n">
-        <v>317.140625</v>
+        <v>339.96875</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="F2" t="n">
-        <v>239693173</v>
+        <v>259133699</v>
       </c>
       <c r="G2" t="n">
-        <v>154628979</v>
+        <v>166373596</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1028228344</v>
+        <v>1123935835</v>
       </c>
       <c r="J2" t="n">
-        <v>998</v>
+        <v>2496</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N2" t="n">
-        <v>6.384521484375</v>
+        <v>6.389026641845703</v>
       </c>
       <c r="O2" t="n">
         <v>59.2</v>
@@ -587,16 +587,16 @@
         <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R2" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T2" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -605,32 +605,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19:25:37</t>
+          <t>11:14:23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10011.15625</v>
+        <v>10655.640625</v>
       </c>
       <c r="C3" t="n">
-        <v>357474.0781249999</v>
+        <v>375397.421875</v>
       </c>
       <c r="D3" t="n">
-        <v>317.140625</v>
+        <v>339.984375</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>239699747</v>
+        <v>259149420</v>
       </c>
       <c r="G3" t="n">
-        <v>154632709</v>
+        <v>166383649</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1028310560</v>
+        <v>1124035491</v>
       </c>
       <c r="J3" t="n">
         <v>2496</v>
@@ -645,25 +645,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N3" t="n">
-        <v>6.401626586914063</v>
+        <v>6.413333892822266</v>
       </c>
       <c r="O3" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="P3" t="n">
         <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R3" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T3" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -672,32 +672,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19:25:38</t>
+          <t>11:14:24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10011.703125</v>
+        <v>10655.90625</v>
       </c>
       <c r="C4" t="n">
-        <v>357481.5156249999</v>
+        <v>375405.09375</v>
       </c>
       <c r="D4" t="n">
-        <v>317.15625</v>
+        <v>339.984375</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>239721915</v>
+        <v>259171018</v>
       </c>
       <c r="G4" t="n">
-        <v>154645021</v>
+        <v>166395685</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1028425437</v>
+        <v>1124145993</v>
       </c>
       <c r="J4" t="n">
         <v>2496</v>
@@ -712,7 +712,7 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N4" t="n">
-        <v>6.399555206298828</v>
+        <v>6.404117584228516</v>
       </c>
       <c r="O4" t="n">
         <v>59.1</v>
@@ -721,16 +721,16 @@
         <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R4" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T4" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -739,32 +739,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19:25:39</t>
+          <t>11:14:25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10011.84375</v>
+        <v>10656.078125</v>
       </c>
       <c r="C5" t="n">
-        <v>357489.2031249999</v>
+        <v>375412.765625</v>
       </c>
       <c r="D5" t="n">
-        <v>317.171875</v>
+        <v>340</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="F5" t="n">
-        <v>239736687</v>
+        <v>259185158</v>
       </c>
       <c r="G5" t="n">
-        <v>154653828</v>
+        <v>166404005</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1028455200</v>
+        <v>1124176686</v>
       </c>
       <c r="J5" t="n">
         <v>2496</v>
@@ -779,7 +779,7 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N5" t="n">
-        <v>6.399738311767578</v>
+        <v>6.405689239501953</v>
       </c>
       <c r="O5" t="n">
         <v>59.1</v>
@@ -788,16 +788,16 @@
         <v>7.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R5" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T5" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -806,32 +806,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:25:40</t>
+          <t>11:14:26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10012.46875</v>
+        <v>10656.765625</v>
       </c>
       <c r="C6" t="n">
-        <v>357496.4374999999</v>
+        <v>375420.015625</v>
       </c>
       <c r="D6" t="n">
-        <v>317.171875</v>
+        <v>340.015625</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>239751509</v>
+        <v>259197427</v>
       </c>
       <c r="G6" t="n">
-        <v>154662057</v>
+        <v>166411259</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1028586960</v>
+        <v>1124286818</v>
       </c>
       <c r="J6" t="n">
         <v>2496</v>
@@ -846,25 +846,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N6" t="n">
-        <v>6.37469482421875</v>
+        <v>6.387401580810547</v>
       </c>
       <c r="O6" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="P6" t="n">
         <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R6" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T6" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -873,32 +873,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19:25:41</t>
+          <t>11:14:27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10012.796875</v>
+        <v>10657.078125</v>
       </c>
       <c r="C7" t="n">
-        <v>357504.1718749999</v>
+        <v>375427.578125</v>
       </c>
       <c r="D7" t="n">
-        <v>317.171875</v>
+        <v>340.015625</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="F7" t="n">
-        <v>239775390</v>
+        <v>259215278</v>
       </c>
       <c r="G7" t="n">
-        <v>154676865</v>
+        <v>166422050</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1028688423</v>
+        <v>1124393361</v>
       </c>
       <c r="J7" t="n">
         <v>2496</v>
@@ -913,7 +913,7 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N7" t="n">
-        <v>6.339828491210938</v>
+        <v>6.343097686767578</v>
       </c>
       <c r="O7" t="n">
         <v>59.5</v>
@@ -922,16 +922,16 @@
         <v>7.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R7" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T7" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -940,32 +940,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19:25:42</t>
+          <t>11:14:28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10013.0625</v>
+        <v>10657.390625</v>
       </c>
       <c r="C8" t="n">
-        <v>357511.7968749999</v>
+        <v>375435.09375</v>
       </c>
       <c r="D8" t="n">
-        <v>317.171875</v>
+        <v>340.015625</v>
       </c>
       <c r="E8" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="F8" t="n">
-        <v>239792965</v>
+        <v>259227900</v>
       </c>
       <c r="G8" t="n">
-        <v>154688043</v>
+        <v>166430876</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1028759257</v>
+        <v>1124459731</v>
       </c>
       <c r="J8" t="n">
         <v>2496</v>
@@ -980,7 +980,7 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N8" t="n">
-        <v>6.301555633544922</v>
+        <v>6.301120758056641</v>
       </c>
       <c r="O8" t="n">
         <v>59.7</v>
@@ -989,16 +989,16 @@
         <v>7.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R8" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T8" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1007,32 +1007,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19:25:43</t>
+          <t>11:14:29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10013.171875</v>
+        <v>10657.65625</v>
       </c>
       <c r="C9" t="n">
-        <v>357519.5312499999</v>
+        <v>375442.71875</v>
       </c>
       <c r="D9" t="n">
-        <v>317.1875</v>
+        <v>340.015625</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="F9" t="n">
-        <v>239805054</v>
+        <v>259242317</v>
       </c>
       <c r="G9" t="n">
-        <v>154695559</v>
+        <v>166439870</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1028841240</v>
+        <v>1124552510</v>
       </c>
       <c r="J9" t="n">
         <v>2496</v>
@@ -1047,25 +1047,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N9" t="n">
-        <v>6.29351806640625</v>
+        <v>6.270381927490234</v>
       </c>
       <c r="O9" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="P9" t="n">
         <v>7.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R9" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T9" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1074,32 +1074,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19:25:44</t>
+          <t>11:14:30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10013.40625</v>
+        <v>10657.734375</v>
       </c>
       <c r="C10" t="n">
-        <v>357527.2031249999</v>
+        <v>375450.703125</v>
       </c>
       <c r="D10" t="n">
-        <v>317.234375</v>
+        <v>340.015625</v>
       </c>
       <c r="E10" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F10" t="n">
-        <v>239822564</v>
+        <v>259245438</v>
       </c>
       <c r="G10" t="n">
-        <v>154705375</v>
+        <v>166441750</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1028908220</v>
+        <v>1124562023</v>
       </c>
       <c r="J10" t="n">
         <v>2496</v>
@@ -1114,7 +1114,7 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N10" t="n">
-        <v>6.278858184814453</v>
+        <v>6.280654907226562</v>
       </c>
       <c r="O10" t="n">
         <v>59.9</v>
@@ -1123,16 +1123,16 @@
         <v>7.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R10" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1141,35 +1141,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19:25:45</t>
+          <t>11:14:31</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10013.984375</v>
+        <v>10658.1875</v>
       </c>
       <c r="C11" t="n">
-        <v>357534.6562499999</v>
+        <v>375458.390625</v>
       </c>
       <c r="D11" t="n">
-        <v>317.25</v>
+        <v>340.015625</v>
       </c>
       <c r="E11" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="F11" t="n">
-        <v>239833292</v>
+        <v>259250062</v>
       </c>
       <c r="G11" t="n">
-        <v>154712005</v>
+        <v>166446217</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1028935737</v>
+        <v>1124611520</v>
       </c>
       <c r="J11" t="n">
-        <v>2496</v>
+        <v>998</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1181,25 +1181,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N11" t="n">
-        <v>6.281078338623047</v>
+        <v>6.305992126464844</v>
       </c>
       <c r="O11" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="P11" t="n">
         <v>7.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R11" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T11" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -1208,32 +1208,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19:25:46</t>
+          <t>11:14:32</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10014.078125</v>
+        <v>10658.265625</v>
       </c>
       <c r="C12" t="n">
-        <v>357542.5468749999</v>
+        <v>375466.296875</v>
       </c>
       <c r="D12" t="n">
-        <v>317.25</v>
+        <v>340.015625</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="F12" t="n">
-        <v>239843517</v>
+        <v>259253620</v>
       </c>
       <c r="G12" t="n">
-        <v>154718040</v>
+        <v>166448458</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1028964745</v>
+        <v>1124625453</v>
       </c>
       <c r="J12" t="n">
         <v>2496</v>
@@ -1248,25 +1248,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N12" t="n">
-        <v>6.284732818603516</v>
+        <v>6.308826446533203</v>
       </c>
       <c r="O12" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="P12" t="n">
         <v>7.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R12" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1275,32 +1275,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19:25:47</t>
+          <t>11:14:33</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10014.234375</v>
+        <v>10658.34375</v>
       </c>
       <c r="C13" t="n">
-        <v>357550.2968749999</v>
+        <v>375474.21875</v>
       </c>
       <c r="D13" t="n">
-        <v>317.296875</v>
+        <v>340.03125</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="F13" t="n">
-        <v>239854323</v>
+        <v>259258315</v>
       </c>
       <c r="G13" t="n">
-        <v>154724800</v>
+        <v>166450887</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1028988403</v>
+        <v>1124641109</v>
       </c>
       <c r="J13" t="n">
         <v>2496</v>
@@ -1315,25 +1315,25 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N13" t="n">
-        <v>6.297016143798828</v>
+        <v>6.308650970458984</v>
       </c>
       <c r="O13" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="P13" t="n">
         <v>7.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R13" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T13" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -1342,32 +1342,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19:25:48</t>
+          <t>11:14:34</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10014.546875</v>
+        <v>10658.5625</v>
       </c>
       <c r="C14" t="n">
-        <v>357557.9218749999</v>
+        <v>375481.9375</v>
       </c>
       <c r="D14" t="n">
-        <v>317.296875</v>
+        <v>340.046875</v>
       </c>
       <c r="E14" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="F14" t="n">
-        <v>239868781</v>
+        <v>259267136</v>
       </c>
       <c r="G14" t="n">
-        <v>154733143</v>
+        <v>166456169</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1029065257</v>
+        <v>1124702205</v>
       </c>
       <c r="J14" t="n">
         <v>2496</v>
@@ -1382,27 +1382,563 @@
         <v>15.6518669128418</v>
       </c>
       <c r="N14" t="n">
-        <v>6.282184600830078</v>
+        <v>6.318038940429688</v>
       </c>
       <c r="O14" t="n">
-        <v>59.9</v>
+        <v>59.6</v>
       </c>
       <c r="P14" t="n">
         <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.409454345703125</v>
+        <v>7.450130462646484</v>
       </c>
       <c r="R14" t="n">
-        <v>0.090545654296875</v>
+        <v>0.0498695373535156</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="T14" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="U14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11:14:35</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10658.71875</v>
+      </c>
+      <c r="C15" t="n">
+        <v>375489.921875</v>
+      </c>
+      <c r="D15" t="n">
+        <v>340.046875</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>259277771</v>
+      </c>
+      <c r="G15" t="n">
+        <v>166462329</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1124728464</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.324565887451172</v>
+      </c>
+      <c r="O15" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>45</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>11:14:36</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10658.8125</v>
+      </c>
+      <c r="C16" t="n">
+        <v>375497.8125</v>
+      </c>
+      <c r="D16" t="n">
+        <v>340.046875</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>259288417</v>
+      </c>
+      <c r="G16" t="n">
+        <v>166468707</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1124755647</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.320037841796875</v>
+      </c>
+      <c r="O16" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>45</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11:14:37</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10659.015625</v>
+      </c>
+      <c r="C17" t="n">
+        <v>375505.6875</v>
+      </c>
+      <c r="D17" t="n">
+        <v>340.0625</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>259298548</v>
+      </c>
+      <c r="G17" t="n">
+        <v>166474608</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1124783791</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.318019866943359</v>
+      </c>
+      <c r="O17" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>45</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11:14:38</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10659.125</v>
+      </c>
+      <c r="C18" t="n">
+        <v>375513.578125</v>
+      </c>
+      <c r="D18" t="n">
+        <v>340.0625</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>259303136</v>
+      </c>
+      <c r="G18" t="n">
+        <v>166477257</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1124798315</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.310317993164063</v>
+      </c>
+      <c r="O18" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>45</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11:14:39</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10659.328125</v>
+      </c>
+      <c r="C19" t="n">
+        <v>375521.328125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>340.0625</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>259313013</v>
+      </c>
+      <c r="G19" t="n">
+        <v>166482829</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1124861742</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.308315277099609</v>
+      </c>
+      <c r="O19" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>45</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>11:14:40</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10659.375</v>
+      </c>
+      <c r="C20" t="n">
+        <v>375529.359375</v>
+      </c>
+      <c r="D20" t="n">
+        <v>340.078125</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>259316578</v>
+      </c>
+      <c r="G20" t="n">
+        <v>166484950</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1124873683</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M20" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.317714691162109</v>
+      </c>
+      <c r="O20" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>45</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11:14:41</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10659.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>375537.265625</v>
+      </c>
+      <c r="D21" t="n">
+        <v>340.078125</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>259320972</v>
+      </c>
+      <c r="G21" t="n">
+        <v>166487457</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1124885303</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.317916870117188</v>
+      </c>
+      <c r="O21" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>45</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11:14:42</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10659.65625</v>
+      </c>
+      <c r="C22" t="n">
+        <v>375545.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>340.078125</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>259324732</v>
+      </c>
+      <c r="G22" t="n">
+        <v>166489651</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1124901462</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2496</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2496</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15.6518669128418</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.319255828857422</v>
+      </c>
+      <c r="O22" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.450130462646484</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.0498695373535156</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>45</v>
+      </c>
+      <c r="U22" t="b">
         <v>0</v>
       </c>
     </row>
